--- a/Assets/SheetXExample/Examples/Exporting Multiple Excel Files/Challenges.xlsx
+++ b/Assets/SheetXExample/Examples/Exporting Multiple Excel Files/Challenges.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="13515" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12180" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="IDs" sheetId="3" r:id="rId1"/>
@@ -140,7 +140,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1122" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1135" uniqueCount="250">
   <si>
     <t>Condition Type</t>
   </si>
@@ -767,6 +767,9 @@
   </si>
   <si>
     <t>fixed</t>
+  </si>
+  <si>
+    <t>doi_ten_header</t>
   </si>
   <si>
     <t>Victory achieved I</t>
@@ -1289,7 +1292,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -1301,77 +1304,12 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thin">
         <color auto="1"/>
       </right>
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -1499,7 +1437,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1511,34 +1449,34 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1623,70 +1561,49 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1705,12 +1622,12 @@
     <cellStyle name="Percent" xfId="3" builtinId="5"/>
     <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
     <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
     <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
     <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
     <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
     <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
@@ -2030,7 +1947,7 @@
     <col min="3" max="3" width="36" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2134,7 +2051,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -2142,7 +2059,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -2150,7 +2067,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -2158,7 +2075,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -2187,7 +2104,7 @@
     <col min="7" max="7" width="29.2857142857143" customWidth="1"/>
     <col min="8" max="8" width="37.5714285714286" customWidth="1"/>
     <col min="9" max="9" width="16.2857142857143" customWidth="1"/>
-    <col min="10" max="10" width="18.4285714285714" style="38" customWidth="1"/>
+    <col min="10" max="10" width="18.4285714285714" style="19" customWidth="1"/>
     <col min="11" max="11" width="43.2857142857143" customWidth="1"/>
     <col min="12" max="12" width="26.2857142857143" customWidth="1"/>
     <col min="13" max="13" width="14.8571428571429" customWidth="1"/>
@@ -2222,7 +2139,7 @@
       <c r="I1" t="s">
         <v>28</v>
       </c>
-      <c r="J1" s="38" t="s">
+      <c r="J1" s="19" t="s">
         <v>29</v>
       </c>
       <c r="K1" t="s">
@@ -2240,10 +2157,10 @@
         <f>B2*100+C2</f>
         <v>101</v>
       </c>
-      <c r="B2" s="40">
+      <c r="B2" s="20">
         <v>1</v>
       </c>
-      <c r="C2" s="28">
+      <c r="C2" s="21">
         <v>1</v>
       </c>
       <c r="D2" t="s">
@@ -2283,10 +2200,10 @@
         <f t="shared" ref="A3:A97" si="0">B3*100+C3</f>
         <v>102</v>
       </c>
-      <c r="B3" s="40">
+      <c r="B3" s="20">
         <v>1</v>
       </c>
-      <c r="C3" s="28">
+      <c r="C3" s="21">
         <v>2</v>
       </c>
       <c r="D3" t="s">
@@ -2326,10 +2243,10 @@
         <f t="shared" si="0"/>
         <v>103</v>
       </c>
-      <c r="B4" s="40">
+      <c r="B4" s="20">
         <v>1</v>
       </c>
-      <c r="C4" s="28">
+      <c r="C4" s="21">
         <v>3</v>
       </c>
       <c r="D4" t="s">
@@ -2369,10 +2286,10 @@
         <f t="shared" si="0"/>
         <v>104</v>
       </c>
-      <c r="B5" s="40">
+      <c r="B5" s="20">
         <v>1</v>
       </c>
-      <c r="C5" s="28">
+      <c r="C5" s="21">
         <v>4</v>
       </c>
       <c r="D5" t="s">
@@ -2412,10 +2329,10 @@
         <f t="shared" si="0"/>
         <v>105</v>
       </c>
-      <c r="B6" s="40">
+      <c r="B6" s="20">
         <v>1</v>
       </c>
-      <c r="C6" s="28">
+      <c r="C6" s="21">
         <v>5</v>
       </c>
       <c r="D6" t="s">
@@ -2455,10 +2372,10 @@
         <f t="shared" si="0"/>
         <v>106</v>
       </c>
-      <c r="B7" s="40">
+      <c r="B7" s="20">
         <v>1</v>
       </c>
-      <c r="C7" s="28">
+      <c r="C7" s="21">
         <v>6</v>
       </c>
       <c r="D7" t="s">
@@ -2498,10 +2415,10 @@
         <f t="shared" ref="A8:A11" si="2">B8*100+C8</f>
         <v>107</v>
       </c>
-      <c r="B8" s="40">
+      <c r="B8" s="20">
         <v>1</v>
       </c>
-      <c r="C8" s="28">
+      <c r="C8" s="21">
         <v>7</v>
       </c>
       <c r="D8" t="s">
@@ -2541,10 +2458,10 @@
         <f t="shared" si="2"/>
         <v>108</v>
       </c>
-      <c r="B9" s="40">
+      <c r="B9" s="20">
         <v>1</v>
       </c>
-      <c r="C9" s="28">
+      <c r="C9" s="21">
         <v>8</v>
       </c>
       <c r="D9" t="s">
@@ -2584,10 +2501,10 @@
         <f t="shared" si="2"/>
         <v>109</v>
       </c>
-      <c r="B10" s="40">
+      <c r="B10" s="20">
         <v>1</v>
       </c>
-      <c r="C10" s="28">
+      <c r="C10" s="21">
         <v>9</v>
       </c>
       <c r="D10" t="s">
@@ -2627,10 +2544,10 @@
         <f t="shared" si="2"/>
         <v>110</v>
       </c>
-      <c r="B11" s="40">
+      <c r="B11" s="20">
         <v>1</v>
       </c>
-      <c r="C11" s="28">
+      <c r="C11" s="21">
         <v>10</v>
       </c>
       <c r="D11" t="s">
@@ -2665,432 +2582,432 @@
         <v>90</v>
       </c>
     </row>
-    <row r="12" s="39" customFormat="1" spans="1:13">
+    <row r="12" s="18" customFormat="1" spans="1:13">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>201</v>
       </c>
-      <c r="B12" s="41">
+      <c r="B12" s="22">
         <v>2</v>
       </c>
-      <c r="C12" s="42">
+      <c r="C12" s="23">
         <v>1</v>
       </c>
-      <c r="D12" s="39" t="s">
+      <c r="D12" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="E12" s="39" t="s">
+      <c r="E12" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="F12" s="39" t="s">
+      <c r="F12" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="G12" s="39" t="s">
+      <c r="G12" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="H12" s="39" t="s">
+      <c r="H12" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="I12" s="39">
+      <c r="I12" s="18">
         <v>1</v>
       </c>
-      <c r="J12" s="43" t="s">
+      <c r="J12" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="K12" s="39" t="s">
+      <c r="K12" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="L12" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="M12" s="39">
+      <c r="L12" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="M12" s="18">
         <f t="shared" ref="M12:M21" si="3">I12*5</f>
         <v>5</v>
       </c>
     </row>
-    <row r="13" s="39" customFormat="1" spans="1:13">
+    <row r="13" s="18" customFormat="1" spans="1:13">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>202</v>
       </c>
-      <c r="B13" s="41">
+      <c r="B13" s="22">
         <v>2</v>
       </c>
-      <c r="C13" s="42">
+      <c r="C13" s="23">
         <v>2</v>
       </c>
-      <c r="D13" s="39" t="s">
+      <c r="D13" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="E13" s="39" t="s">
+      <c r="E13" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="F13" s="39" t="s">
+      <c r="F13" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="G13" s="39" t="s">
+      <c r="G13" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="H13" s="39" t="s">
+      <c r="H13" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="I13" s="39">
+      <c r="I13" s="18">
         <v>5</v>
       </c>
-      <c r="J13" s="43" t="s">
+      <c r="J13" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="K13" s="39" t="s">
+      <c r="K13" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="L13" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="M13" s="39">
+      <c r="L13" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="M13" s="18">
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
     </row>
-    <row r="14" s="39" customFormat="1" spans="1:13">
+    <row r="14" s="18" customFormat="1" spans="1:13">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>203</v>
       </c>
-      <c r="B14" s="41">
+      <c r="B14" s="22">
         <v>2</v>
       </c>
-      <c r="C14" s="42">
+      <c r="C14" s="23">
         <v>3</v>
       </c>
-      <c r="D14" s="39" t="s">
+      <c r="D14" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="E14" s="39" t="s">
+      <c r="E14" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="F14" s="39" t="s">
+      <c r="F14" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="G14" s="39" t="s">
+      <c r="G14" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="H14" s="39" t="s">
+      <c r="H14" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="I14" s="39">
+      <c r="I14" s="18">
         <v>10</v>
       </c>
-      <c r="J14" s="43" t="s">
+      <c r="J14" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="K14" s="39" t="s">
+      <c r="K14" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="L14" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="M14" s="39">
+      <c r="L14" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="M14" s="18">
         <f t="shared" si="3"/>
         <v>50</v>
       </c>
     </row>
-    <row r="15" s="39" customFormat="1" spans="1:13">
+    <row r="15" s="18" customFormat="1" spans="1:13">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>204</v>
       </c>
-      <c r="B15" s="41">
+      <c r="B15" s="22">
         <v>2</v>
       </c>
-      <c r="C15" s="42">
+      <c r="C15" s="23">
         <v>4</v>
       </c>
-      <c r="D15" s="39" t="s">
+      <c r="D15" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="E15" s="39" t="s">
+      <c r="E15" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="F15" s="39" t="s">
+      <c r="F15" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="G15" s="39" t="s">
+      <c r="G15" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="H15" s="39" t="s">
+      <c r="H15" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="I15" s="39">
+      <c r="I15" s="18">
         <v>15</v>
       </c>
-      <c r="J15" s="43" t="s">
+      <c r="J15" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="K15" s="39" t="s">
+      <c r="K15" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="L15" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="M15" s="39">
+      <c r="L15" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="M15" s="18">
         <f t="shared" si="3"/>
         <v>75</v>
       </c>
     </row>
-    <row r="16" s="39" customFormat="1" spans="1:13">
+    <row r="16" s="18" customFormat="1" spans="1:13">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>205</v>
       </c>
-      <c r="B16" s="41">
+      <c r="B16" s="22">
         <v>2</v>
       </c>
-      <c r="C16" s="42">
+      <c r="C16" s="23">
         <v>5</v>
       </c>
-      <c r="D16" s="39" t="s">
+      <c r="D16" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="E16" s="39" t="s">
+      <c r="E16" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="F16" s="39" t="s">
+      <c r="F16" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="G16" s="39" t="s">
+      <c r="G16" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="H16" s="39" t="s">
+      <c r="H16" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="I16" s="39">
+      <c r="I16" s="18">
         <v>20</v>
       </c>
-      <c r="J16" s="43" t="s">
+      <c r="J16" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="K16" s="39" t="s">
+      <c r="K16" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="L16" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="M16" s="39">
+      <c r="L16" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="M16" s="18">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
     </row>
-    <row r="17" s="39" customFormat="1" spans="1:13">
+    <row r="17" s="18" customFormat="1" spans="1:16">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>206</v>
       </c>
-      <c r="B17" s="41">
+      <c r="B17" s="22">
         <v>2</v>
       </c>
-      <c r="C17" s="42">
+      <c r="C17" s="23">
         <v>6</v>
       </c>
-      <c r="D17" s="39" t="s">
+      <c r="D17" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="E17" s="39" t="s">
+      <c r="E17" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="F17" s="39" t="s">
+      <c r="F17" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="G17" s="39" t="s">
+      <c r="G17" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="H17" s="39" t="s">
+      <c r="H17" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="I17" s="39">
+      <c r="I17" s="18">
         <v>25</v>
       </c>
-      <c r="J17" s="43" t="s">
+      <c r="J17" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="K17" s="39" t="s">
+      <c r="K17" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="L17" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="M17" s="39">
+      <c r="L17" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="M17" s="18">
         <f t="shared" si="3"/>
         <v>125</v>
       </c>
     </row>
-    <row r="18" s="39" customFormat="1" spans="1:13">
+    <row r="18" s="18" customFormat="1" spans="1:16">
       <c r="A18">
         <f t="shared" ref="A18:A21" si="4">B18*100+C18</f>
         <v>207</v>
       </c>
-      <c r="B18" s="41">
+      <c r="B18" s="22">
         <v>2</v>
       </c>
-      <c r="C18" s="42">
+      <c r="C18" s="23">
         <v>7</v>
       </c>
-      <c r="D18" s="39" t="s">
+      <c r="D18" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="E18" s="39" t="s">
+      <c r="E18" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="F18" s="39" t="s">
+      <c r="F18" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="G18" s="39" t="s">
+      <c r="G18" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="H18" s="39" t="s">
+      <c r="H18" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="I18" s="39">
+      <c r="I18" s="18">
         <v>30</v>
       </c>
-      <c r="J18" s="43" t="s">
+      <c r="J18" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="K18" s="39" t="s">
+      <c r="K18" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="L18" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="M18" s="39">
+      <c r="L18" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="M18" s="18">
         <f t="shared" si="3"/>
         <v>150</v>
       </c>
     </row>
-    <row r="19" s="39" customFormat="1" spans="1:13">
+    <row r="19" s="18" customFormat="1" spans="1:16">
       <c r="A19">
         <f t="shared" si="4"/>
         <v>208</v>
       </c>
-      <c r="B19" s="41">
+      <c r="B19" s="22">
         <v>2</v>
       </c>
-      <c r="C19" s="42">
+      <c r="C19" s="23">
         <v>8</v>
       </c>
-      <c r="D19" s="39" t="s">
+      <c r="D19" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="E19" s="39" t="s">
+      <c r="E19" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="F19" s="39" t="s">
+      <c r="F19" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="G19" s="39" t="s">
+      <c r="G19" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="H19" s="39" t="s">
+      <c r="H19" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="I19" s="39">
+      <c r="I19" s="18">
         <v>35</v>
       </c>
-      <c r="J19" s="43" t="s">
+      <c r="J19" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="K19" s="39" t="s">
+      <c r="K19" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="L19" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="M19" s="39">
+      <c r="L19" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="M19" s="18">
         <f t="shared" si="3"/>
         <v>175</v>
       </c>
     </row>
-    <row r="20" s="39" customFormat="1" spans="1:13">
+    <row r="20" s="18" customFormat="1" spans="1:16">
       <c r="A20">
         <f t="shared" si="4"/>
         <v>209</v>
       </c>
-      <c r="B20" s="41">
+      <c r="B20" s="22">
         <v>2</v>
       </c>
-      <c r="C20" s="42">
+      <c r="C20" s="23">
         <v>9</v>
       </c>
-      <c r="D20" s="39" t="s">
+      <c r="D20" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="E20" s="39" t="s">
+      <c r="E20" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="F20" s="39" t="s">
+      <c r="F20" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="G20" s="39" t="s">
+      <c r="G20" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="H20" s="39" t="s">
+      <c r="H20" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="I20" s="39">
+      <c r="I20" s="18">
         <v>40</v>
       </c>
-      <c r="J20" s="43" t="s">
+      <c r="J20" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="K20" s="39" t="s">
+      <c r="K20" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="L20" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="M20" s="39">
+      <c r="L20" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="M20" s="18">
         <f t="shared" si="3"/>
         <v>200</v>
       </c>
     </row>
-    <row r="21" s="39" customFormat="1" spans="1:13">
+    <row r="21" s="18" customFormat="1" spans="1:16">
       <c r="A21">
         <f t="shared" si="4"/>
         <v>210</v>
       </c>
-      <c r="B21" s="41">
+      <c r="B21" s="22">
         <v>2</v>
       </c>
-      <c r="C21" s="42">
+      <c r="C21" s="23">
         <v>10</v>
       </c>
-      <c r="D21" s="39" t="s">
+      <c r="D21" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="E21" s="39" t="s">
+      <c r="E21" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="F21" s="39" t="s">
+      <c r="F21" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="G21" s="39" t="s">
+      <c r="G21" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="H21" s="39" t="s">
+      <c r="H21" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="I21" s="39">
+      <c r="I21" s="18">
         <v>45</v>
       </c>
-      <c r="J21" s="43" t="s">
+      <c r="J21" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="K21" s="39" t="s">
+      <c r="K21" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="L21" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="M21" s="39">
+      <c r="L21" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="M21" s="18">
         <f t="shared" si="3"/>
         <v>225</v>
       </c>
@@ -3100,10 +3017,10 @@
         <f t="shared" si="0"/>
         <v>301</v>
       </c>
-      <c r="B22" s="40">
+      <c r="B22" s="20">
         <v>3</v>
       </c>
-      <c r="C22" s="28">
+      <c r="C22" s="21">
         <v>1</v>
       </c>
       <c r="D22" t="s">
@@ -3124,13 +3041,13 @@
       <c r="I22">
         <v>1</v>
       </c>
-      <c r="J22" s="38">
+      <c r="J22" s="19">
         <v>1</v>
       </c>
       <c r="K22" t="s">
         <v>67</v>
       </c>
-      <c r="L22" s="44" t="s">
+      <c r="L22" s="25" t="s">
         <v>68</v>
       </c>
       <c r="M22" t="str">
@@ -3154,10 +3071,10 @@
         <f t="shared" si="0"/>
         <v>302</v>
       </c>
-      <c r="B23" s="40">
+      <c r="B23" s="20">
         <v>3</v>
       </c>
-      <c r="C23" s="28">
+      <c r="C23" s="21">
         <v>2</v>
       </c>
       <c r="D23" t="s">
@@ -3178,13 +3095,13 @@
       <c r="I23">
         <v>1</v>
       </c>
-      <c r="J23" s="38">
+      <c r="J23" s="19">
         <v>2</v>
       </c>
       <c r="K23" t="s">
         <v>67</v>
       </c>
-      <c r="L23" s="44" t="s">
+      <c r="L23" s="25" t="s">
         <v>70</v>
       </c>
       <c r="M23" t="str">
@@ -3208,10 +3125,10 @@
         <f t="shared" si="0"/>
         <v>303</v>
       </c>
-      <c r="B24" s="40">
+      <c r="B24" s="20">
         <v>3</v>
       </c>
-      <c r="C24" s="28">
+      <c r="C24" s="21">
         <v>3</v>
       </c>
       <c r="D24" t="s">
@@ -3232,13 +3149,13 @@
       <c r="I24">
         <v>1</v>
       </c>
-      <c r="J24" s="38">
+      <c r="J24" s="19">
         <v>3</v>
       </c>
       <c r="K24" t="s">
         <v>67</v>
       </c>
-      <c r="L24" s="44" t="s">
+      <c r="L24" s="25" t="s">
         <v>72</v>
       </c>
       <c r="M24" t="str">
@@ -3262,10 +3179,10 @@
         <f t="shared" si="0"/>
         <v>304</v>
       </c>
-      <c r="B25" s="40">
+      <c r="B25" s="20">
         <v>3</v>
       </c>
-      <c r="C25" s="28">
+      <c r="C25" s="21">
         <v>4</v>
       </c>
       <c r="D25" t="s">
@@ -3286,13 +3203,13 @@
       <c r="I25">
         <v>1</v>
       </c>
-      <c r="J25" s="38">
+      <c r="J25" s="19">
         <v>4</v>
       </c>
       <c r="K25" t="s">
         <v>67</v>
       </c>
-      <c r="L25" s="44" t="s">
+      <c r="L25" s="25" t="s">
         <v>74</v>
       </c>
       <c r="M25" t="str">
@@ -3316,10 +3233,10 @@
         <f t="shared" si="0"/>
         <v>305</v>
       </c>
-      <c r="B26" s="40">
+      <c r="B26" s="20">
         <v>3</v>
       </c>
-      <c r="C26" s="28">
+      <c r="C26" s="21">
         <v>5</v>
       </c>
       <c r="D26" t="s">
@@ -3340,13 +3257,13 @@
       <c r="I26">
         <v>1</v>
       </c>
-      <c r="J26" s="38">
+      <c r="J26" s="19">
         <v>5</v>
       </c>
       <c r="K26" t="s">
         <v>67</v>
       </c>
-      <c r="L26" s="44" t="s">
+      <c r="L26" s="25" t="s">
         <v>76</v>
       </c>
       <c r="M26" t="str">
@@ -3370,10 +3287,10 @@
         <f t="shared" si="0"/>
         <v>306</v>
       </c>
-      <c r="B27" s="40">
+      <c r="B27" s="20">
         <v>3</v>
       </c>
-      <c r="C27" s="28">
+      <c r="C27" s="21">
         <v>6</v>
       </c>
       <c r="D27" t="s">
@@ -3394,13 +3311,13 @@
       <c r="I27">
         <v>1</v>
       </c>
-      <c r="J27" s="38">
+      <c r="J27" s="19">
         <v>6</v>
       </c>
       <c r="K27" t="s">
         <v>67</v>
       </c>
-      <c r="L27" s="44" t="s">
+      <c r="L27" s="25" t="s">
         <v>78</v>
       </c>
       <c r="M27" t="str">
@@ -3424,10 +3341,10 @@
         <f t="shared" si="0"/>
         <v>307</v>
       </c>
-      <c r="B28" s="40">
+      <c r="B28" s="20">
         <v>3</v>
       </c>
-      <c r="C28" s="28">
+      <c r="C28" s="21">
         <v>7</v>
       </c>
       <c r="D28" t="s">
@@ -3448,13 +3365,13 @@
       <c r="I28">
         <v>1</v>
       </c>
-      <c r="J28" s="38">
+      <c r="J28" s="19">
         <v>7</v>
       </c>
       <c r="K28" t="s">
         <v>67</v>
       </c>
-      <c r="L28" s="44" t="s">
+      <c r="L28" s="25" t="s">
         <v>80</v>
       </c>
       <c r="M28" t="str">
@@ -3478,10 +3395,10 @@
         <f t="shared" si="0"/>
         <v>308</v>
       </c>
-      <c r="B29" s="40">
+      <c r="B29" s="20">
         <v>3</v>
       </c>
-      <c r="C29" s="28">
+      <c r="C29" s="21">
         <v>8</v>
       </c>
       <c r="D29" t="s">
@@ -3502,13 +3419,13 @@
       <c r="I29">
         <v>1</v>
       </c>
-      <c r="J29" s="38">
+      <c r="J29" s="19">
         <v>8</v>
       </c>
       <c r="K29" t="s">
         <v>67</v>
       </c>
-      <c r="L29" s="44" t="s">
+      <c r="L29" s="25" t="s">
         <v>82</v>
       </c>
       <c r="M29" t="str">
@@ -3532,10 +3449,10 @@
         <f t="shared" si="0"/>
         <v>309</v>
       </c>
-      <c r="B30" s="40">
+      <c r="B30" s="20">
         <v>3</v>
       </c>
-      <c r="C30" s="28">
+      <c r="C30" s="21">
         <v>9</v>
       </c>
       <c r="D30" t="s">
@@ -3556,13 +3473,13 @@
       <c r="I30">
         <v>1</v>
       </c>
-      <c r="J30" s="38">
+      <c r="J30" s="19">
         <v>9</v>
       </c>
       <c r="K30" t="s">
         <v>67</v>
       </c>
-      <c r="L30" s="44" t="s">
+      <c r="L30" s="25" t="s">
         <v>84</v>
       </c>
       <c r="M30" t="str">
@@ -3586,10 +3503,10 @@
         <f t="shared" si="0"/>
         <v>310</v>
       </c>
-      <c r="B31" s="40">
+      <c r="B31" s="20">
         <v>3</v>
       </c>
-      <c r="C31" s="28">
+      <c r="C31" s="21">
         <v>10</v>
       </c>
       <c r="D31" t="s">
@@ -3610,13 +3527,13 @@
       <c r="I31">
         <v>1</v>
       </c>
-      <c r="J31" s="38">
+      <c r="J31" s="19">
         <v>10</v>
       </c>
       <c r="K31" t="s">
         <v>67</v>
       </c>
-      <c r="L31" s="44" t="s">
+      <c r="L31" s="25" t="s">
         <v>86</v>
       </c>
       <c r="M31" t="str">
@@ -3640,10 +3557,10 @@
         <f t="shared" si="0"/>
         <v>311</v>
       </c>
-      <c r="B32" s="40">
+      <c r="B32" s="20">
         <v>3</v>
       </c>
-      <c r="C32" s="28">
+      <c r="C32" s="21">
         <v>11</v>
       </c>
       <c r="D32" t="s">
@@ -3664,13 +3581,13 @@
       <c r="I32">
         <v>1</v>
       </c>
-      <c r="J32" s="38">
+      <c r="J32" s="19">
         <v>11</v>
       </c>
       <c r="K32" t="s">
         <v>67</v>
       </c>
-      <c r="L32" s="44" t="s">
+      <c r="L32" s="25" t="s">
         <v>88</v>
       </c>
       <c r="M32" t="str">
@@ -3694,10 +3611,10 @@
         <f t="shared" si="0"/>
         <v>312</v>
       </c>
-      <c r="B33" s="40">
+      <c r="B33" s="20">
         <v>3</v>
       </c>
-      <c r="C33" s="28">
+      <c r="C33" s="21">
         <v>12</v>
       </c>
       <c r="D33" t="s">
@@ -3718,13 +3635,13 @@
       <c r="I33">
         <v>1</v>
       </c>
-      <c r="J33" s="38">
+      <c r="J33" s="19">
         <v>12</v>
       </c>
       <c r="K33" t="s">
         <v>67</v>
       </c>
-      <c r="L33" s="44" t="s">
+      <c r="L33" s="25" t="s">
         <v>90</v>
       </c>
       <c r="M33" t="str">
@@ -3748,10 +3665,10 @@
         <f t="shared" si="0"/>
         <v>313</v>
       </c>
-      <c r="B34" s="40">
+      <c r="B34" s="20">
         <v>3</v>
       </c>
-      <c r="C34" s="28">
+      <c r="C34" s="21">
         <v>13</v>
       </c>
       <c r="D34" t="s">
@@ -3772,13 +3689,13 @@
       <c r="I34">
         <v>1</v>
       </c>
-      <c r="J34" s="38">
+      <c r="J34" s="19">
         <v>13</v>
       </c>
       <c r="K34" t="s">
         <v>67</v>
       </c>
-      <c r="L34" s="44" t="s">
+      <c r="L34" s="25" t="s">
         <v>92</v>
       </c>
       <c r="M34" t="str">
@@ -3802,10 +3719,10 @@
         <f t="shared" si="0"/>
         <v>314</v>
       </c>
-      <c r="B35" s="40">
+      <c r="B35" s="20">
         <v>3</v>
       </c>
-      <c r="C35" s="28">
+      <c r="C35" s="21">
         <v>14</v>
       </c>
       <c r="D35" t="s">
@@ -3826,13 +3743,13 @@
       <c r="I35">
         <v>1</v>
       </c>
-      <c r="J35" s="38">
+      <c r="J35" s="19">
         <v>14</v>
       </c>
       <c r="K35" t="s">
         <v>67</v>
       </c>
-      <c r="L35" s="44" t="s">
+      <c r="L35" s="25" t="s">
         <v>94</v>
       </c>
       <c r="M35" t="str">
@@ -3856,10 +3773,10 @@
         <f t="shared" si="0"/>
         <v>315</v>
       </c>
-      <c r="B36" s="40">
+      <c r="B36" s="20">
         <v>3</v>
       </c>
-      <c r="C36" s="28">
+      <c r="C36" s="21">
         <v>15</v>
       </c>
       <c r="D36" t="s">
@@ -3880,13 +3797,13 @@
       <c r="I36">
         <v>1</v>
       </c>
-      <c r="J36" s="38">
+      <c r="J36" s="19">
         <v>15</v>
       </c>
       <c r="K36" t="s">
         <v>67</v>
       </c>
-      <c r="L36" s="44" t="s">
+      <c r="L36" s="25" t="s">
         <v>96</v>
       </c>
       <c r="M36" t="str">
@@ -3910,10 +3827,10 @@
         <f t="shared" si="0"/>
         <v>316</v>
       </c>
-      <c r="B37" s="40">
+      <c r="B37" s="20">
         <v>3</v>
       </c>
-      <c r="C37" s="28">
+      <c r="C37" s="21">
         <v>16</v>
       </c>
       <c r="D37" t="s">
@@ -3934,13 +3851,13 @@
       <c r="I37">
         <v>1</v>
       </c>
-      <c r="J37" s="38">
+      <c r="J37" s="19">
         <v>16</v>
       </c>
       <c r="K37" t="s">
         <v>67</v>
       </c>
-      <c r="L37" s="44" t="s">
+      <c r="L37" s="25" t="s">
         <v>98</v>
       </c>
       <c r="M37" t="str">
@@ -3959,455 +3876,455 @@
         <v>40</v>
       </c>
     </row>
-    <row r="38" s="39" customFormat="1" spans="1:14">
+    <row r="38" s="18" customFormat="1" spans="1:16">
       <c r="A38">
         <f t="shared" si="0"/>
         <v>401</v>
       </c>
-      <c r="B38" s="41">
+      <c r="B38" s="22">
         <v>4</v>
       </c>
-      <c r="C38" s="42">
+      <c r="C38" s="23">
         <v>1</v>
       </c>
-      <c r="D38" s="39" t="s">
+      <c r="D38" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="E38" s="39" t="s">
+      <c r="E38" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="F38" s="39" t="s">
+      <c r="F38" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="G38" s="39" t="s">
+      <c r="G38" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="H38" s="39" t="s">
+      <c r="H38" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="I38" s="39">
+      <c r="I38" s="18">
         <v>500</v>
       </c>
-      <c r="J38" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="K38" s="39" t="s">
+      <c r="J38" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="K38" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="L38" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="M38" s="43">
+      <c r="L38" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="M38" s="24">
         <f>I38/100</f>
         <v>5</v>
       </c>
-      <c r="N38" s="43"/>
-    </row>
-    <row r="39" s="39" customFormat="1" spans="1:14">
+      <c r="N38" s="24"/>
+    </row>
+    <row r="39" s="18" customFormat="1" spans="1:16">
       <c r="A39">
         <f t="shared" si="0"/>
         <v>402</v>
       </c>
-      <c r="B39" s="41">
+      <c r="B39" s="22">
         <v>4</v>
       </c>
-      <c r="C39" s="42">
+      <c r="C39" s="23">
         <v>2</v>
       </c>
-      <c r="D39" s="39" t="s">
+      <c r="D39" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="E39" s="39" t="s">
+      <c r="E39" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="F39" s="39" t="s">
+      <c r="F39" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="G39" s="39" t="s">
+      <c r="G39" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="H39" s="39" t="s">
+      <c r="H39" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="I39" s="39">
+      <c r="I39" s="18">
         <v>1000</v>
       </c>
-      <c r="J39" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="K39" s="39" t="s">
+      <c r="J39" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="K39" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="L39" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="M39" s="43">
+      <c r="L39" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="M39" s="24">
         <f t="shared" ref="M39:M47" si="8">I39/100</f>
         <v>10</v>
       </c>
-      <c r="N39" s="43"/>
-    </row>
-    <row r="40" s="39" customFormat="1" spans="1:14">
+      <c r="N39" s="24"/>
+    </row>
+    <row r="40" s="18" customFormat="1" spans="1:16">
       <c r="A40">
         <f t="shared" si="0"/>
         <v>403</v>
       </c>
-      <c r="B40" s="41">
+      <c r="B40" s="22">
         <v>4</v>
       </c>
-      <c r="C40" s="42">
+      <c r="C40" s="23">
         <v>3</v>
       </c>
-      <c r="D40" s="39" t="s">
+      <c r="D40" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="E40" s="39" t="s">
+      <c r="E40" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="F40" s="39" t="s">
+      <c r="F40" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="G40" s="39" t="s">
+      <c r="G40" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="H40" s="39" t="s">
+      <c r="H40" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="I40" s="39">
+      <c r="I40" s="18">
         <v>2000</v>
       </c>
-      <c r="J40" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="K40" s="39" t="s">
+      <c r="J40" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="K40" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="L40" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="M40" s="43">
+      <c r="L40" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="M40" s="24">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="N40" s="43"/>
-    </row>
-    <row r="41" s="39" customFormat="1" spans="1:14">
+      <c r="N40" s="24"/>
+    </row>
+    <row r="41" s="18" customFormat="1" spans="1:16">
       <c r="A41">
         <f t="shared" si="0"/>
         <v>404</v>
       </c>
-      <c r="B41" s="41">
+      <c r="B41" s="22">
         <v>4</v>
       </c>
-      <c r="C41" s="42">
+      <c r="C41" s="23">
         <v>4</v>
       </c>
-      <c r="D41" s="39" t="s">
+      <c r="D41" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="E41" s="39" t="s">
+      <c r="E41" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="F41" s="39" t="s">
+      <c r="F41" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="G41" s="39" t="s">
+      <c r="G41" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="H41" s="39" t="s">
+      <c r="H41" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="I41" s="39">
+      <c r="I41" s="18">
         <v>4000</v>
       </c>
-      <c r="J41" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="K41" s="39" t="s">
+      <c r="J41" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="K41" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="L41" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="M41" s="43">
+      <c r="L41" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="M41" s="24">
         <f t="shared" si="8"/>
         <v>40</v>
       </c>
-      <c r="N41" s="43"/>
-    </row>
-    <row r="42" s="39" customFormat="1" spans="1:14">
+      <c r="N41" s="24"/>
+    </row>
+    <row r="42" s="18" customFormat="1" spans="1:16">
       <c r="A42">
         <f t="shared" si="0"/>
         <v>405</v>
       </c>
-      <c r="B42" s="41">
+      <c r="B42" s="22">
         <v>4</v>
       </c>
-      <c r="C42" s="42">
+      <c r="C42" s="23">
         <v>5</v>
       </c>
-      <c r="D42" s="39" t="s">
+      <c r="D42" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="E42" s="39" t="s">
+      <c r="E42" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="F42" s="39" t="s">
+      <c r="F42" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="G42" s="39" t="s">
+      <c r="G42" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="H42" s="39" t="s">
+      <c r="H42" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="I42" s="39">
+      <c r="I42" s="18">
         <v>8000</v>
       </c>
-      <c r="J42" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="K42" s="39" t="s">
+      <c r="J42" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="K42" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="L42" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="M42" s="43">
+      <c r="L42" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="M42" s="24">
         <f t="shared" si="8"/>
         <v>80</v>
       </c>
-      <c r="N42" s="43"/>
-    </row>
-    <row r="43" s="39" customFormat="1" spans="1:14">
+      <c r="N42" s="24"/>
+    </row>
+    <row r="43" s="18" customFormat="1" spans="1:16">
       <c r="A43">
         <f t="shared" si="0"/>
         <v>406</v>
       </c>
-      <c r="B43" s="41">
+      <c r="B43" s="22">
         <v>4</v>
       </c>
-      <c r="C43" s="42">
+      <c r="C43" s="23">
         <v>6</v>
       </c>
-      <c r="D43" s="39" t="s">
+      <c r="D43" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="E43" s="39" t="s">
+      <c r="E43" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="F43" s="39" t="s">
+      <c r="F43" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="G43" s="39" t="s">
+      <c r="G43" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="H43" s="39" t="s">
+      <c r="H43" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="I43" s="39">
+      <c r="I43" s="18">
         <v>16000</v>
       </c>
-      <c r="J43" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="K43" s="39" t="s">
+      <c r="J43" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="K43" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="L43" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="M43" s="43">
+      <c r="L43" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="M43" s="24">
         <f t="shared" si="8"/>
         <v>160</v>
       </c>
-      <c r="N43" s="43"/>
-    </row>
-    <row r="44" s="39" customFormat="1" spans="1:14">
+      <c r="N43" s="24"/>
+    </row>
+    <row r="44" s="18" customFormat="1" spans="1:16">
       <c r="A44">
         <f t="shared" si="0"/>
         <v>407</v>
       </c>
-      <c r="B44" s="41">
+      <c r="B44" s="22">
         <v>4</v>
       </c>
-      <c r="C44" s="42">
+      <c r="C44" s="23">
         <v>7</v>
       </c>
-      <c r="D44" s="39" t="s">
+      <c r="D44" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="E44" s="39" t="s">
+      <c r="E44" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="F44" s="39" t="s">
+      <c r="F44" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="G44" s="39" t="s">
+      <c r="G44" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="H44" s="39" t="s">
+      <c r="H44" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="I44" s="39">
+      <c r="I44" s="18">
         <v>32000</v>
       </c>
-      <c r="J44" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="K44" s="39" t="s">
+      <c r="J44" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="K44" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="L44" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="M44" s="43">
+      <c r="L44" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="M44" s="24">
         <f t="shared" si="8"/>
         <v>320</v>
       </c>
-      <c r="N44" s="43"/>
-    </row>
-    <row r="45" s="39" customFormat="1" spans="1:14">
+      <c r="N44" s="24"/>
+    </row>
+    <row r="45" s="18" customFormat="1" spans="1:16">
       <c r="A45">
         <f t="shared" ref="A45:A47" si="9">B45*100+C45</f>
         <v>408</v>
       </c>
-      <c r="B45" s="41">
+      <c r="B45" s="22">
         <v>4</v>
       </c>
-      <c r="C45" s="42">
+      <c r="C45" s="23">
         <v>8</v>
       </c>
-      <c r="D45" s="39" t="s">
+      <c r="D45" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="E45" s="39" t="s">
+      <c r="E45" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="F45" s="39" t="s">
+      <c r="F45" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="G45" s="39" t="s">
+      <c r="G45" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="H45" s="39" t="s">
+      <c r="H45" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="I45" s="39">
+      <c r="I45" s="18">
         <v>64000</v>
       </c>
-      <c r="J45" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="K45" s="39" t="s">
+      <c r="J45" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="K45" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="L45" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="M45" s="43">
+      <c r="L45" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="M45" s="24">
         <f t="shared" si="8"/>
         <v>640</v>
       </c>
-      <c r="N45" s="43"/>
-    </row>
-    <row r="46" s="39" customFormat="1" spans="1:14">
+      <c r="N45" s="24"/>
+    </row>
+    <row r="46" s="18" customFormat="1" spans="1:16">
       <c r="A46">
         <f t="shared" si="9"/>
         <v>409</v>
       </c>
-      <c r="B46" s="41">
+      <c r="B46" s="22">
         <v>4</v>
       </c>
-      <c r="C46" s="42">
+      <c r="C46" s="23">
         <v>9</v>
       </c>
-      <c r="D46" s="39" t="s">
+      <c r="D46" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="E46" s="39" t="s">
+      <c r="E46" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="F46" s="39" t="s">
+      <c r="F46" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="G46" s="39" t="s">
+      <c r="G46" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="H46" s="39" t="s">
+      <c r="H46" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="I46" s="39">
+      <c r="I46" s="18">
         <v>128000</v>
       </c>
-      <c r="J46" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="K46" s="39" t="s">
+      <c r="J46" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="K46" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="L46" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="M46" s="43">
+      <c r="L46" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="M46" s="24">
         <f t="shared" si="8"/>
         <v>1280</v>
       </c>
-      <c r="N46" s="43"/>
-    </row>
-    <row r="47" s="39" customFormat="1" spans="1:14">
+      <c r="N46" s="24"/>
+    </row>
+    <row r="47" s="18" customFormat="1" spans="1:16">
       <c r="A47">
         <f t="shared" si="9"/>
         <v>410</v>
       </c>
-      <c r="B47" s="41">
+      <c r="B47" s="22">
         <v>4</v>
       </c>
-      <c r="C47" s="42">
+      <c r="C47" s="23">
         <v>10</v>
       </c>
-      <c r="D47" s="39" t="s">
+      <c r="D47" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="E47" s="39" t="s">
+      <c r="E47" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="F47" s="39" t="s">
+      <c r="F47" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="G47" s="39" t="s">
+      <c r="G47" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="H47" s="39" t="s">
+      <c r="H47" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="I47" s="39">
+      <c r="I47" s="18">
         <v>256000</v>
       </c>
-      <c r="J47" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="K47" s="39" t="s">
+      <c r="J47" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="K47" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="L47" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="M47" s="43">
+      <c r="L47" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="M47" s="24">
         <f t="shared" si="8"/>
         <v>2560</v>
       </c>
-      <c r="N47" s="43"/>
-    </row>
-    <row r="48" spans="1:15">
+      <c r="N47" s="24"/>
+    </row>
+    <row r="48" spans="1:16">
       <c r="A48">
         <f t="shared" si="0"/>
         <v>501</v>
       </c>
-      <c r="B48" s="40">
+      <c r="B48" s="20">
         <v>5</v>
       </c>
-      <c r="C48" s="28">
+      <c r="C48" s="21">
         <v>1</v>
       </c>
       <c r="D48" t="s">
@@ -4428,13 +4345,13 @@
       <c r="I48">
         <v>5</v>
       </c>
-      <c r="J48" s="38" t="s">
+      <c r="J48" s="19" t="s">
         <v>103</v>
       </c>
       <c r="K48" t="s">
         <v>67</v>
       </c>
-      <c r="L48" s="44" t="s">
+      <c r="L48" s="25" t="s">
         <v>70</v>
       </c>
       <c r="M48" t="str">
@@ -4454,10 +4371,10 @@
         <f t="shared" si="0"/>
         <v>502</v>
       </c>
-      <c r="B49" s="40">
+      <c r="B49" s="20">
         <v>5</v>
       </c>
-      <c r="C49" s="28">
+      <c r="C49" s="21">
         <v>2</v>
       </c>
       <c r="D49" t="s">
@@ -4478,13 +4395,13 @@
       <c r="I49">
         <v>10</v>
       </c>
-      <c r="J49" s="38" t="s">
+      <c r="J49" s="19" t="s">
         <v>103</v>
       </c>
       <c r="K49" t="s">
         <v>67</v>
       </c>
-      <c r="L49" s="44" t="s">
+      <c r="L49" s="25" t="s">
         <v>74</v>
       </c>
       <c r="M49" t="str">
@@ -4504,10 +4421,10 @@
         <f t="shared" si="0"/>
         <v>503</v>
       </c>
-      <c r="B50" s="40">
+      <c r="B50" s="20">
         <v>5</v>
       </c>
-      <c r="C50" s="28">
+      <c r="C50" s="21">
         <v>3</v>
       </c>
       <c r="D50" t="s">
@@ -4528,13 +4445,13 @@
       <c r="I50">
         <v>20</v>
       </c>
-      <c r="J50" s="38" t="s">
+      <c r="J50" s="19" t="s">
         <v>103</v>
       </c>
       <c r="K50" t="s">
         <v>67</v>
       </c>
-      <c r="L50" s="44" t="s">
+      <c r="L50" s="25" t="s">
         <v>82</v>
       </c>
       <c r="M50" t="str">
@@ -4554,10 +4471,10 @@
         <f t="shared" si="0"/>
         <v>504</v>
       </c>
-      <c r="B51" s="40">
+      <c r="B51" s="20">
         <v>5</v>
       </c>
-      <c r="C51" s="28">
+      <c r="C51" s="21">
         <v>4</v>
       </c>
       <c r="D51" t="s">
@@ -4578,13 +4495,13 @@
       <c r="I51">
         <v>30</v>
       </c>
-      <c r="J51" s="38" t="s">
+      <c r="J51" s="19" t="s">
         <v>103</v>
       </c>
       <c r="K51" t="s">
         <v>67</v>
       </c>
-      <c r="L51" s="44" t="s">
+      <c r="L51" s="25" t="s">
         <v>90</v>
       </c>
       <c r="M51" t="str">
@@ -4604,10 +4521,10 @@
         <f t="shared" si="0"/>
         <v>505</v>
       </c>
-      <c r="B52" s="40">
+      <c r="B52" s="20">
         <v>5</v>
       </c>
-      <c r="C52" s="28">
+      <c r="C52" s="21">
         <v>5</v>
       </c>
       <c r="D52" t="s">
@@ -4628,13 +4545,13 @@
       <c r="I52">
         <v>40</v>
       </c>
-      <c r="J52" s="38" t="s">
+      <c r="J52" s="19" t="s">
         <v>103</v>
       </c>
       <c r="K52" t="s">
         <v>67</v>
       </c>
-      <c r="L52" s="44" t="s">
+      <c r="L52" s="25" t="s">
         <v>98</v>
       </c>
       <c r="M52" t="str">
@@ -4654,10 +4571,10 @@
         <f t="shared" si="0"/>
         <v>506</v>
       </c>
-      <c r="B53" s="40">
+      <c r="B53" s="20">
         <v>5</v>
       </c>
-      <c r="C53" s="28">
+      <c r="C53" s="21">
         <v>6</v>
       </c>
       <c r="D53" t="s">
@@ -4678,13 +4595,13 @@
       <c r="I53">
         <v>50</v>
       </c>
-      <c r="J53" s="38" t="s">
+      <c r="J53" s="19" t="s">
         <v>103</v>
       </c>
       <c r="K53" t="s">
         <v>67</v>
       </c>
-      <c r="L53" s="44" t="s">
+      <c r="L53" s="25" t="s">
         <v>119</v>
       </c>
       <c r="M53" t="str">
@@ -4704,10 +4621,10 @@
         <f t="shared" si="0"/>
         <v>507</v>
       </c>
-      <c r="B54" s="40">
+      <c r="B54" s="20">
         <v>5</v>
       </c>
-      <c r="C54" s="28">
+      <c r="C54" s="21">
         <v>7</v>
       </c>
       <c r="D54" t="s">
@@ -4728,13 +4645,13 @@
       <c r="I54">
         <v>60</v>
       </c>
-      <c r="J54" s="38" t="s">
+      <c r="J54" s="19" t="s">
         <v>103</v>
       </c>
       <c r="K54" t="s">
         <v>67</v>
       </c>
-      <c r="L54" s="44" t="s">
+      <c r="L54" s="25" t="s">
         <v>121</v>
       </c>
       <c r="M54" t="str">
@@ -4749,433 +4666,433 @@
         <v>60</v>
       </c>
     </row>
-    <row r="55" s="39" customFormat="1" spans="1:13">
+    <row r="55" s="18" customFormat="1" spans="1:15">
       <c r="A55">
         <f t="shared" si="0"/>
         <v>601</v>
       </c>
-      <c r="B55" s="41">
+      <c r="B55" s="22">
         <v>6</v>
       </c>
-      <c r="C55" s="42">
+      <c r="C55" s="23">
         <v>1</v>
       </c>
-      <c r="D55" s="39" t="s">
+      <c r="D55" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="E55" s="39" t="s">
+      <c r="E55" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="F55" s="39" t="s">
+      <c r="F55" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="G55" s="39" t="s">
+      <c r="G55" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="H55" s="39" t="s">
+      <c r="H55" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="I55" s="39">
+      <c r="I55" s="18">
         <v>5</v>
       </c>
-      <c r="J55" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="K55" s="39" t="s">
+      <c r="J55" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="K55" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="L55" s="39">
+      <c r="L55" s="18">
         <f>I55/2.5</f>
         <v>2</v>
       </c>
-      <c r="M55" s="39">
+      <c r="M55" s="18">
         <v>8</v>
       </c>
     </row>
-    <row r="56" s="39" customFormat="1" spans="1:13">
+    <row r="56" s="18" customFormat="1" spans="1:15">
       <c r="A56">
         <f t="shared" si="0"/>
         <v>602</v>
       </c>
-      <c r="B56" s="41">
+      <c r="B56" s="22">
         <v>6</v>
       </c>
-      <c r="C56" s="42">
+      <c r="C56" s="23">
         <v>2</v>
       </c>
-      <c r="D56" s="39" t="s">
+      <c r="D56" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="E56" s="39" t="s">
+      <c r="E56" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="F56" s="39" t="s">
+      <c r="F56" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="G56" s="39" t="s">
+      <c r="G56" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="H56" s="39" t="s">
+      <c r="H56" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="I56" s="39">
+      <c r="I56" s="18">
         <v>15</v>
       </c>
-      <c r="J56" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="K56" s="39" t="s">
+      <c r="J56" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="K56" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="L56" s="39">
+      <c r="L56" s="18">
         <f t="shared" ref="L56:L60" si="12">I56/2.5</f>
         <v>6</v>
       </c>
-      <c r="M56" s="39">
+      <c r="M56" s="18">
         <v>8</v>
       </c>
     </row>
-    <row r="57" s="39" customFormat="1" spans="1:13">
+    <row r="57" s="18" customFormat="1" spans="1:15">
       <c r="A57">
         <f t="shared" si="0"/>
         <v>603</v>
       </c>
-      <c r="B57" s="41">
+      <c r="B57" s="22">
         <v>6</v>
       </c>
-      <c r="C57" s="42">
+      <c r="C57" s="23">
         <v>3</v>
       </c>
-      <c r="D57" s="39" t="s">
+      <c r="D57" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="E57" s="39" t="s">
+      <c r="E57" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="F57" s="39" t="s">
+      <c r="F57" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="G57" s="39" t="s">
+      <c r="G57" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="H57" s="39" t="s">
+      <c r="H57" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="I57" s="39">
+      <c r="I57" s="18">
         <v>30</v>
       </c>
-      <c r="J57" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="K57" s="39" t="s">
+      <c r="J57" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="K57" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="L57" s="39">
+      <c r="L57" s="18">
         <f t="shared" si="12"/>
         <v>12</v>
       </c>
-      <c r="M57" s="39">
+      <c r="M57" s="18">
         <v>8</v>
       </c>
     </row>
-    <row r="58" s="39" customFormat="1" spans="1:13">
+    <row r="58" s="18" customFormat="1" spans="1:15">
       <c r="A58">
         <f t="shared" si="0"/>
         <v>604</v>
       </c>
-      <c r="B58" s="41">
+      <c r="B58" s="22">
         <v>6</v>
       </c>
-      <c r="C58" s="42">
+      <c r="C58" s="23">
         <v>4</v>
       </c>
-      <c r="D58" s="39" t="s">
+      <c r="D58" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="E58" s="39" t="s">
+      <c r="E58" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="F58" s="39" t="s">
+      <c r="F58" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="G58" s="39" t="s">
+      <c r="G58" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="H58" s="39" t="s">
+      <c r="H58" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="I58" s="39">
+      <c r="I58" s="18">
         <v>60</v>
       </c>
-      <c r="J58" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="K58" s="39" t="s">
+      <c r="J58" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="K58" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="L58" s="39">
+      <c r="L58" s="18">
         <f t="shared" si="12"/>
         <v>24</v>
       </c>
-      <c r="M58" s="39">
+      <c r="M58" s="18">
         <v>8</v>
       </c>
     </row>
-    <row r="59" s="39" customFormat="1" spans="1:13">
+    <row r="59" s="18" customFormat="1" spans="1:15">
       <c r="A59">
         <f t="shared" si="0"/>
         <v>605</v>
       </c>
-      <c r="B59" s="41">
+      <c r="B59" s="22">
         <v>6</v>
       </c>
-      <c r="C59" s="42">
+      <c r="C59" s="23">
         <v>5</v>
       </c>
-      <c r="D59" s="39" t="s">
+      <c r="D59" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="E59" s="39" t="s">
+      <c r="E59" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="F59" s="39" t="s">
+      <c r="F59" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="G59" s="39" t="s">
+      <c r="G59" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="H59" s="39" t="s">
+      <c r="H59" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="I59" s="39">
+      <c r="I59" s="18">
         <v>90</v>
       </c>
-      <c r="J59" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="K59" s="39" t="s">
+      <c r="J59" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="K59" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="L59" s="39">
+      <c r="L59" s="18">
         <f t="shared" si="12"/>
         <v>36</v>
       </c>
-      <c r="M59" s="39">
+      <c r="M59" s="18">
         <v>8</v>
       </c>
     </row>
-    <row r="60" s="39" customFormat="1" spans="1:13">
+    <row r="60" s="18" customFormat="1" spans="1:15">
       <c r="A60">
         <f t="shared" ref="A60:A64" si="13">B60*100+C60</f>
         <v>606</v>
       </c>
-      <c r="B60" s="41">
+      <c r="B60" s="22">
         <v>6</v>
       </c>
-      <c r="C60" s="42">
+      <c r="C60" s="23">
         <v>6</v>
       </c>
-      <c r="D60" s="39" t="s">
+      <c r="D60" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="E60" s="39" t="s">
+      <c r="E60" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="F60" s="39" t="s">
+      <c r="F60" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="G60" s="39" t="s">
+      <c r="G60" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="H60" s="39" t="s">
+      <c r="H60" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="I60" s="39">
+      <c r="I60" s="18">
         <v>120</v>
       </c>
-      <c r="J60" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="K60" s="39" t="s">
+      <c r="J60" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="K60" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="L60" s="39">
+      <c r="L60" s="18">
         <f t="shared" si="12"/>
         <v>48</v>
       </c>
-      <c r="M60" s="39">
+      <c r="M60" s="18">
         <v>8</v>
       </c>
     </row>
-    <row r="61" s="39" customFormat="1" spans="1:13">
+    <row r="61" s="18" customFormat="1" spans="1:15">
       <c r="A61">
         <f t="shared" si="13"/>
         <v>607</v>
       </c>
-      <c r="B61" s="41">
+      <c r="B61" s="22">
         <v>6</v>
       </c>
-      <c r="C61" s="42">
+      <c r="C61" s="23">
         <v>7</v>
       </c>
-      <c r="D61" s="39" t="s">
+      <c r="D61" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="E61" s="39" t="s">
+      <c r="E61" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="F61" s="39" t="s">
+      <c r="F61" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="G61" s="39" t="s">
+      <c r="G61" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="H61" s="39" t="s">
+      <c r="H61" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="I61" s="39">
+      <c r="I61" s="18">
         <v>150</v>
       </c>
-      <c r="J61" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="K61" s="39" t="s">
+      <c r="J61" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="K61" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="L61" s="39">
+      <c r="L61" s="18">
         <f t="shared" ref="L61:L64" si="14">I61/2.5</f>
         <v>60</v>
       </c>
-      <c r="M61" s="39">
+      <c r="M61" s="18">
         <v>8</v>
       </c>
     </row>
-    <row r="62" s="39" customFormat="1" spans="1:13">
+    <row r="62" s="18" customFormat="1" spans="1:15">
       <c r="A62">
         <f t="shared" si="13"/>
         <v>608</v>
       </c>
-      <c r="B62" s="41">
+      <c r="B62" s="22">
         <v>6</v>
       </c>
-      <c r="C62" s="42">
+      <c r="C62" s="23">
         <v>8</v>
       </c>
-      <c r="D62" s="39" t="s">
+      <c r="D62" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="E62" s="39" t="s">
+      <c r="E62" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="F62" s="39" t="s">
+      <c r="F62" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="G62" s="39" t="s">
+      <c r="G62" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="H62" s="39" t="s">
+      <c r="H62" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="I62" s="39">
+      <c r="I62" s="18">
         <v>180</v>
       </c>
-      <c r="J62" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="K62" s="39" t="s">
+      <c r="J62" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="K62" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="L62" s="39">
+      <c r="L62" s="18">
         <f t="shared" si="14"/>
         <v>72</v>
       </c>
-      <c r="M62" s="39">
+      <c r="M62" s="18">
         <v>8</v>
       </c>
     </row>
-    <row r="63" s="39" customFormat="1" spans="1:13">
+    <row r="63" s="18" customFormat="1" spans="1:15">
       <c r="A63">
         <f t="shared" si="13"/>
         <v>609</v>
       </c>
-      <c r="B63" s="41">
+      <c r="B63" s="22">
         <v>6</v>
       </c>
-      <c r="C63" s="42">
+      <c r="C63" s="23">
         <v>9</v>
       </c>
-      <c r="D63" s="39" t="s">
+      <c r="D63" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="E63" s="39" t="s">
+      <c r="E63" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="F63" s="39" t="s">
+      <c r="F63" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="G63" s="39" t="s">
+      <c r="G63" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="H63" s="39" t="s">
+      <c r="H63" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="I63" s="39">
+      <c r="I63" s="18">
         <v>210</v>
       </c>
-      <c r="J63" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="K63" s="39" t="s">
+      <c r="J63" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="K63" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="L63" s="39">
+      <c r="L63" s="18">
         <f t="shared" si="14"/>
         <v>84</v>
       </c>
-      <c r="M63" s="39">
+      <c r="M63" s="18">
         <v>8</v>
       </c>
     </row>
-    <row r="64" s="39" customFormat="1" spans="1:13">
+    <row r="64" s="18" customFormat="1" spans="1:15">
       <c r="A64">
         <f t="shared" si="13"/>
         <v>610</v>
       </c>
-      <c r="B64" s="41">
+      <c r="B64" s="22">
         <v>6</v>
       </c>
-      <c r="C64" s="42">
+      <c r="C64" s="23">
         <v>10</v>
       </c>
-      <c r="D64" s="39" t="s">
+      <c r="D64" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="E64" s="39" t="s">
+      <c r="E64" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="F64" s="39" t="s">
+      <c r="F64" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="G64" s="39" t="s">
+      <c r="G64" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="H64" s="39" t="s">
+      <c r="H64" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="I64" s="39">
+      <c r="I64" s="18">
         <v>240</v>
       </c>
-      <c r="J64" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="K64" s="39" t="s">
+      <c r="J64" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="K64" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="L64" s="39">
+      <c r="L64" s="18">
         <f t="shared" si="14"/>
         <v>96</v>
       </c>
-      <c r="M64" s="39">
+      <c r="M64" s="18">
         <v>8</v>
       </c>
     </row>
@@ -5184,10 +5101,10 @@
         <f t="shared" si="0"/>
         <v>701</v>
       </c>
-      <c r="B65" s="40">
+      <c r="B65" s="20">
         <v>7</v>
       </c>
-      <c r="C65" s="28">
+      <c r="C65" s="21">
         <v>1</v>
       </c>
       <c r="D65" t="s">
@@ -5208,7 +5125,7 @@
       <c r="I65">
         <v>10</v>
       </c>
-      <c r="J65" s="38" t="s">
+      <c r="J65" s="19" t="s">
         <v>103</v>
       </c>
       <c r="K65" t="s">
@@ -5227,10 +5144,10 @@
         <f t="shared" si="0"/>
         <v>702</v>
       </c>
-      <c r="B66" s="40">
+      <c r="B66" s="20">
         <v>7</v>
       </c>
-      <c r="C66" s="28">
+      <c r="C66" s="21">
         <v>2</v>
       </c>
       <c r="D66" t="s">
@@ -5251,7 +5168,7 @@
       <c r="I66">
         <v>20</v>
       </c>
-      <c r="J66" s="38" t="s">
+      <c r="J66" s="19" t="s">
         <v>103</v>
       </c>
       <c r="K66" t="s">
@@ -5270,10 +5187,10 @@
         <f t="shared" si="0"/>
         <v>703</v>
       </c>
-      <c r="B67" s="40">
+      <c r="B67" s="20">
         <v>7</v>
       </c>
-      <c r="C67" s="28">
+      <c r="C67" s="21">
         <v>3</v>
       </c>
       <c r="D67" t="s">
@@ -5294,7 +5211,7 @@
       <c r="I67">
         <v>30</v>
       </c>
-      <c r="J67" s="38" t="s">
+      <c r="J67" s="19" t="s">
         <v>103</v>
       </c>
       <c r="K67" t="s">
@@ -5313,10 +5230,10 @@
         <f t="shared" si="0"/>
         <v>704</v>
       </c>
-      <c r="B68" s="40">
+      <c r="B68" s="20">
         <v>7</v>
       </c>
-      <c r="C68" s="28">
+      <c r="C68" s="21">
         <v>4</v>
       </c>
       <c r="D68" t="s">
@@ -5337,7 +5254,7 @@
       <c r="I68">
         <v>40</v>
       </c>
-      <c r="J68" s="38" t="s">
+      <c r="J68" s="19" t="s">
         <v>103</v>
       </c>
       <c r="K68" t="s">
@@ -5356,10 +5273,10 @@
         <f t="shared" si="0"/>
         <v>705</v>
       </c>
-      <c r="B69" s="40">
+      <c r="B69" s="20">
         <v>7</v>
       </c>
-      <c r="C69" s="28">
+      <c r="C69" s="21">
         <v>5</v>
       </c>
       <c r="D69" t="s">
@@ -5380,7 +5297,7 @@
       <c r="I69">
         <v>50</v>
       </c>
-      <c r="J69" s="38" t="s">
+      <c r="J69" s="19" t="s">
         <v>103</v>
       </c>
       <c r="K69" t="s">
@@ -5399,10 +5316,10 @@
         <f t="shared" ref="A70" si="16">B70*100+C70</f>
         <v>706</v>
       </c>
-      <c r="B70" s="40">
+      <c r="B70" s="20">
         <v>7</v>
       </c>
-      <c r="C70" s="28">
+      <c r="C70" s="21">
         <v>6</v>
       </c>
       <c r="D70" t="s">
@@ -5423,7 +5340,7 @@
       <c r="I70">
         <v>60</v>
       </c>
-      <c r="J70" s="38" t="s">
+      <c r="J70" s="19" t="s">
         <v>103</v>
       </c>
       <c r="K70" t="s">
@@ -5442,10 +5359,10 @@
         <f t="shared" ref="A71" si="17">B71*100+C71</f>
         <v>707</v>
       </c>
-      <c r="B71" s="40">
+      <c r="B71" s="20">
         <v>7</v>
       </c>
-      <c r="C71" s="28">
+      <c r="C71" s="21">
         <v>7</v>
       </c>
       <c r="D71" t="s">
@@ -5466,7 +5383,7 @@
       <c r="I71">
         <v>70</v>
       </c>
-      <c r="J71" s="38" t="s">
+      <c r="J71" s="19" t="s">
         <v>103</v>
       </c>
       <c r="K71" t="s">
@@ -5485,10 +5402,10 @@
         <f t="shared" ref="A72" si="18">B72*100+C72</f>
         <v>708</v>
       </c>
-      <c r="B72" s="40">
+      <c r="B72" s="20">
         <v>7</v>
       </c>
-      <c r="C72" s="28">
+      <c r="C72" s="21">
         <v>8</v>
       </c>
       <c r="D72" t="s">
@@ -5509,7 +5426,7 @@
       <c r="I72">
         <v>80</v>
       </c>
-      <c r="J72" s="38" t="s">
+      <c r="J72" s="19" t="s">
         <v>103</v>
       </c>
       <c r="K72" t="s">
@@ -5528,10 +5445,10 @@
         <f t="shared" ref="A73" si="19">B73*100+C73</f>
         <v>709</v>
       </c>
-      <c r="B73" s="40">
+      <c r="B73" s="20">
         <v>7</v>
       </c>
-      <c r="C73" s="28">
+      <c r="C73" s="21">
         <v>9</v>
       </c>
       <c r="D73" t="s">
@@ -5552,7 +5469,7 @@
       <c r="I73">
         <v>90</v>
       </c>
-      <c r="J73" s="38" t="s">
+      <c r="J73" s="19" t="s">
         <v>103</v>
       </c>
       <c r="K73" t="s">
@@ -5571,10 +5488,10 @@
         <f t="shared" ref="A74" si="20">B74*100+C74</f>
         <v>710</v>
       </c>
-      <c r="B74" s="40">
+      <c r="B74" s="20">
         <v>7</v>
       </c>
-      <c r="C74" s="28">
+      <c r="C74" s="21">
         <v>10</v>
       </c>
       <c r="D74" t="s">
@@ -5595,7 +5512,7 @@
       <c r="I74">
         <v>100</v>
       </c>
-      <c r="J74" s="38" t="s">
+      <c r="J74" s="19" t="s">
         <v>103</v>
       </c>
       <c r="K74" t="s">
@@ -5609,435 +5526,435 @@
         <v>10</v>
       </c>
     </row>
-    <row r="75" s="39" customFormat="1" spans="1:13">
+    <row r="75" s="18" customFormat="1" spans="1:13">
       <c r="A75">
         <f t="shared" si="0"/>
         <v>801</v>
       </c>
-      <c r="B75" s="41">
+      <c r="B75" s="22">
         <v>8</v>
       </c>
-      <c r="C75" s="42">
+      <c r="C75" s="23">
         <v>1</v>
       </c>
-      <c r="D75" s="39" t="s">
+      <c r="D75" s="18" t="s">
         <v>149</v>
       </c>
       <c r="E75" t="s">
         <v>150</v>
       </c>
-      <c r="F75" s="39" t="s">
+      <c r="F75" s="18" t="s">
         <v>151</v>
       </c>
       <c r="G75" t="s">
         <v>152</v>
       </c>
-      <c r="H75" s="39" t="s">
+      <c r="H75" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="I75" s="39">
+      <c r="I75" s="18">
         <v>100</v>
       </c>
-      <c r="J75" s="43" t="s">
-        <v>39</v>
-      </c>
-      <c r="K75" s="39" t="s">
+      <c r="J75" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="K75" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="L75" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="M75" s="39">
+      <c r="L75" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="M75" s="18">
         <f>I75/25</f>
         <v>4</v>
       </c>
     </row>
-    <row r="76" s="39" customFormat="1" spans="1:13">
+    <row r="76" s="18" customFormat="1" spans="1:13">
       <c r="A76">
         <f t="shared" si="0"/>
         <v>802</v>
       </c>
-      <c r="B76" s="41">
+      <c r="B76" s="22">
         <v>8</v>
       </c>
-      <c r="C76" s="42">
+      <c r="C76" s="23">
         <v>2</v>
       </c>
-      <c r="D76" s="39" t="s">
+      <c r="D76" s="18" t="s">
         <v>153</v>
       </c>
       <c r="E76" t="s">
         <v>150</v>
       </c>
-      <c r="F76" s="39" t="s">
+      <c r="F76" s="18" t="s">
         <v>151</v>
       </c>
       <c r="G76" t="s">
         <v>152</v>
       </c>
-      <c r="H76" s="39" t="s">
+      <c r="H76" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="I76" s="39">
+      <c r="I76" s="18">
         <v>200</v>
       </c>
-      <c r="J76" s="43" t="s">
-        <v>39</v>
-      </c>
-      <c r="K76" s="39" t="s">
+      <c r="J76" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="K76" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="L76" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="M76" s="39">
+      <c r="L76" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="M76" s="18">
         <f t="shared" ref="M76:M84" si="21">I76/25</f>
         <v>8</v>
       </c>
     </row>
-    <row r="77" s="39" customFormat="1" spans="1:13">
+    <row r="77" s="18" customFormat="1" spans="1:13">
       <c r="A77">
         <f t="shared" si="0"/>
         <v>803</v>
       </c>
-      <c r="B77" s="41">
+      <c r="B77" s="22">
         <v>8</v>
       </c>
-      <c r="C77" s="42">
+      <c r="C77" s="23">
         <v>3</v>
       </c>
-      <c r="D77" s="39" t="s">
+      <c r="D77" s="18" t="s">
         <v>154</v>
       </c>
       <c r="E77" t="s">
         <v>150</v>
       </c>
-      <c r="F77" s="39" t="s">
+      <c r="F77" s="18" t="s">
         <v>151</v>
       </c>
       <c r="G77" t="s">
         <v>152</v>
       </c>
-      <c r="H77" s="39" t="s">
+      <c r="H77" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="I77" s="39">
+      <c r="I77" s="18">
         <v>400</v>
       </c>
-      <c r="J77" s="43" t="s">
-        <v>39</v>
-      </c>
-      <c r="K77" s="39" t="s">
+      <c r="J77" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="K77" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="L77" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="M77" s="39">
+      <c r="L77" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="M77" s="18">
         <f t="shared" si="21"/>
         <v>16</v>
       </c>
     </row>
-    <row r="78" s="39" customFormat="1" spans="1:13">
+    <row r="78" s="18" customFormat="1" spans="1:13">
       <c r="A78">
         <f t="shared" si="0"/>
         <v>804</v>
       </c>
-      <c r="B78" s="41">
+      <c r="B78" s="22">
         <v>8</v>
       </c>
-      <c r="C78" s="42">
+      <c r="C78" s="23">
         <v>4</v>
       </c>
-      <c r="D78" s="39" t="s">
+      <c r="D78" s="18" t="s">
         <v>155</v>
       </c>
       <c r="E78" t="s">
         <v>150</v>
       </c>
-      <c r="F78" s="39" t="s">
+      <c r="F78" s="18" t="s">
         <v>151</v>
       </c>
       <c r="G78" t="s">
         <v>152</v>
       </c>
-      <c r="H78" s="39" t="s">
+      <c r="H78" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="I78" s="39">
+      <c r="I78" s="18">
         <v>800</v>
       </c>
-      <c r="J78" s="43" t="s">
-        <v>39</v>
-      </c>
-      <c r="K78" s="39" t="s">
+      <c r="J78" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="K78" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="L78" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="M78" s="39">
+      <c r="L78" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="M78" s="18">
         <f t="shared" si="21"/>
         <v>32</v>
       </c>
     </row>
-    <row r="79" s="39" customFormat="1" spans="1:13">
+    <row r="79" s="18" customFormat="1" spans="1:13">
       <c r="A79">
         <f t="shared" si="0"/>
         <v>805</v>
       </c>
-      <c r="B79" s="41">
+      <c r="B79" s="22">
         <v>8</v>
       </c>
-      <c r="C79" s="42">
+      <c r="C79" s="23">
         <v>5</v>
       </c>
-      <c r="D79" s="39" t="s">
+      <c r="D79" s="18" t="s">
         <v>156</v>
       </c>
       <c r="E79" t="s">
         <v>150</v>
       </c>
-      <c r="F79" s="39" t="s">
+      <c r="F79" s="18" t="s">
         <v>151</v>
       </c>
       <c r="G79" t="s">
         <v>152</v>
       </c>
-      <c r="H79" s="39" t="s">
+      <c r="H79" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="I79" s="39">
+      <c r="I79" s="18">
         <v>1600</v>
       </c>
-      <c r="J79" s="43" t="s">
-        <v>39</v>
-      </c>
-      <c r="K79" s="39" t="s">
+      <c r="J79" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="K79" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="L79" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="M79" s="39">
+      <c r="L79" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="M79" s="18">
         <f t="shared" si="21"/>
         <v>64</v>
       </c>
     </row>
-    <row r="80" s="39" customFormat="1" spans="1:13">
+    <row r="80" s="18" customFormat="1" spans="1:13">
       <c r="A80">
         <f t="shared" ref="A80" si="22">B80*100+C80</f>
         <v>806</v>
       </c>
-      <c r="B80" s="41">
+      <c r="B80" s="22">
         <v>8</v>
       </c>
-      <c r="C80" s="42">
+      <c r="C80" s="23">
         <v>6</v>
       </c>
-      <c r="D80" s="39" t="s">
+      <c r="D80" s="18" t="s">
         <v>157</v>
       </c>
       <c r="E80" t="s">
         <v>150</v>
       </c>
-      <c r="F80" s="39" t="s">
+      <c r="F80" s="18" t="s">
         <v>151</v>
       </c>
       <c r="G80" t="s">
         <v>152</v>
       </c>
-      <c r="H80" s="39" t="s">
+      <c r="H80" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="I80" s="39">
+      <c r="I80" s="18">
         <v>3200</v>
       </c>
-      <c r="J80" s="43" t="s">
-        <v>39</v>
-      </c>
-      <c r="K80" s="39" t="s">
+      <c r="J80" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="K80" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="L80" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="M80" s="39">
+      <c r="L80" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="M80" s="18">
         <f t="shared" si="21"/>
         <v>128</v>
       </c>
     </row>
-    <row r="81" s="39" customFormat="1" spans="1:13">
+    <row r="81" s="18" customFormat="1" spans="1:13">
       <c r="A81">
         <f t="shared" ref="A81:A83" si="23">B81*100+C81</f>
         <v>807</v>
       </c>
-      <c r="B81" s="41">
+      <c r="B81" s="22">
         <v>8</v>
       </c>
-      <c r="C81" s="42">
+      <c r="C81" s="23">
         <v>7</v>
       </c>
-      <c r="D81" s="39" t="s">
+      <c r="D81" s="18" t="s">
         <v>158</v>
       </c>
       <c r="E81" t="s">
         <v>150</v>
       </c>
-      <c r="F81" s="39" t="s">
+      <c r="F81" s="18" t="s">
         <v>151</v>
       </c>
       <c r="G81" t="s">
         <v>152</v>
       </c>
-      <c r="H81" s="39" t="s">
+      <c r="H81" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="I81" s="39">
+      <c r="I81" s="18">
         <v>6400</v>
       </c>
-      <c r="J81" s="43" t="s">
-        <v>39</v>
-      </c>
-      <c r="K81" s="39" t="s">
+      <c r="J81" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="K81" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="L81" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="M81" s="39">
+      <c r="L81" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="M81" s="18">
         <f t="shared" si="21"/>
         <v>256</v>
       </c>
     </row>
-    <row r="82" s="39" customFormat="1" spans="1:13">
+    <row r="82" s="18" customFormat="1" spans="1:13">
       <c r="A82">
         <f t="shared" si="23"/>
         <v>808</v>
       </c>
-      <c r="B82" s="41">
+      <c r="B82" s="22">
         <v>8</v>
       </c>
-      <c r="C82" s="42">
+      <c r="C82" s="23">
         <v>8</v>
       </c>
-      <c r="D82" s="39" t="s">
+      <c r="D82" s="18" t="s">
         <v>159</v>
       </c>
       <c r="E82" t="s">
         <v>150</v>
       </c>
-      <c r="F82" s="39" t="s">
+      <c r="F82" s="18" t="s">
         <v>151</v>
       </c>
       <c r="G82" t="s">
         <v>152</v>
       </c>
-      <c r="H82" s="39" t="s">
+      <c r="H82" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="I82" s="39">
+      <c r="I82" s="18">
         <f>I81*2</f>
         <v>12800</v>
       </c>
-      <c r="J82" s="43" t="s">
-        <v>39</v>
-      </c>
-      <c r="K82" s="39" t="s">
+      <c r="J82" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="K82" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="L82" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="M82" s="39">
+      <c r="L82" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="M82" s="18">
         <f t="shared" si="21"/>
         <v>512</v>
       </c>
     </row>
-    <row r="83" s="39" customFormat="1" spans="1:13">
+    <row r="83" s="18" customFormat="1" spans="1:13">
       <c r="A83">
         <f t="shared" si="23"/>
         <v>809</v>
       </c>
-      <c r="B83" s="41">
+      <c r="B83" s="22">
         <v>8</v>
       </c>
-      <c r="C83" s="42">
+      <c r="C83" s="23">
         <v>9</v>
       </c>
-      <c r="D83" s="39" t="s">
+      <c r="D83" s="18" t="s">
         <v>160</v>
       </c>
       <c r="E83" t="s">
         <v>150</v>
       </c>
-      <c r="F83" s="39" t="s">
+      <c r="F83" s="18" t="s">
         <v>151</v>
       </c>
       <c r="G83" t="s">
         <v>152</v>
       </c>
-      <c r="H83" s="39" t="s">
+      <c r="H83" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="I83" s="39">
+      <c r="I83" s="18">
         <f>I82*2</f>
         <v>25600</v>
       </c>
-      <c r="J83" s="43" t="s">
-        <v>39</v>
-      </c>
-      <c r="K83" s="39" t="s">
+      <c r="J83" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="K83" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="L83" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="M83" s="39">
+      <c r="L83" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="M83" s="18">
         <f t="shared" si="21"/>
         <v>1024</v>
       </c>
     </row>
-    <row r="84" s="39" customFormat="1" spans="1:13">
+    <row r="84" s="18" customFormat="1" spans="1:13">
       <c r="A84">
         <f t="shared" ref="A84" si="24">B84*100+C84</f>
         <v>810</v>
       </c>
-      <c r="B84" s="41">
+      <c r="B84" s="22">
         <v>8</v>
       </c>
-      <c r="C84" s="42">
+      <c r="C84" s="23">
         <v>10</v>
       </c>
-      <c r="D84" s="39" t="s">
+      <c r="D84" s="18" t="s">
         <v>161</v>
       </c>
       <c r="E84" t="s">
         <v>150</v>
       </c>
-      <c r="F84" s="39" t="s">
+      <c r="F84" s="18" t="s">
         <v>151</v>
       </c>
       <c r="G84" t="s">
         <v>152</v>
       </c>
-      <c r="H84" s="39" t="s">
+      <c r="H84" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="I84" s="39">
+      <c r="I84" s="18">
         <f>I83*2</f>
         <v>51200</v>
       </c>
-      <c r="J84" s="43" t="s">
-        <v>39</v>
-      </c>
-      <c r="K84" s="39" t="s">
+      <c r="J84" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="K84" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="L84" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="M84" s="39">
+      <c r="L84" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="M84" s="18">
         <f t="shared" si="21"/>
         <v>2048</v>
       </c>
@@ -6047,10 +5964,10 @@
         <f t="shared" si="0"/>
         <v>901</v>
       </c>
-      <c r="B85" s="40">
+      <c r="B85" s="20">
         <v>9</v>
       </c>
-      <c r="C85" s="28">
+      <c r="C85" s="21">
         <v>1</v>
       </c>
       <c r="D85" t="s">
@@ -6071,7 +5988,7 @@
       <c r="I85">
         <v>40000</v>
       </c>
-      <c r="J85" s="38" t="s">
+      <c r="J85" s="19" t="s">
         <v>166</v>
       </c>
       <c r="K85" t="s">
@@ -6090,10 +6007,10 @@
         <f t="shared" si="0"/>
         <v>902</v>
       </c>
-      <c r="B86" s="40">
+      <c r="B86" s="20">
         <v>9</v>
       </c>
-      <c r="C86" s="28">
+      <c r="C86" s="21">
         <v>2</v>
       </c>
       <c r="D86" t="s">
@@ -6114,7 +6031,7 @@
       <c r="I86">
         <v>80000</v>
       </c>
-      <c r="J86" s="38" t="s">
+      <c r="J86" s="19" t="s">
         <v>166</v>
       </c>
       <c r="K86" t="s">
@@ -6133,10 +6050,10 @@
         <f t="shared" si="0"/>
         <v>903</v>
       </c>
-      <c r="B87" s="40">
+      <c r="B87" s="20">
         <v>9</v>
       </c>
-      <c r="C87" s="28">
+      <c r="C87" s="21">
         <v>3</v>
       </c>
       <c r="D87" t="s">
@@ -6157,7 +6074,7 @@
       <c r="I87">
         <v>160000</v>
       </c>
-      <c r="J87" s="38" t="s">
+      <c r="J87" s="19" t="s">
         <v>166</v>
       </c>
       <c r="K87" t="s">
@@ -6176,10 +6093,10 @@
         <f t="shared" si="0"/>
         <v>904</v>
       </c>
-      <c r="B88" s="40">
+      <c r="B88" s="20">
         <v>9</v>
       </c>
-      <c r="C88" s="28">
+      <c r="C88" s="21">
         <v>4</v>
       </c>
       <c r="D88" t="s">
@@ -6200,7 +6117,7 @@
       <c r="I88">
         <v>320000</v>
       </c>
-      <c r="J88" s="38" t="s">
+      <c r="J88" s="19" t="s">
         <v>166</v>
       </c>
       <c r="K88" t="s">
@@ -6219,10 +6136,10 @@
         <f t="shared" si="0"/>
         <v>905</v>
       </c>
-      <c r="B89" s="40">
+      <c r="B89" s="20">
         <v>9</v>
       </c>
-      <c r="C89" s="28">
+      <c r="C89" s="21">
         <v>5</v>
       </c>
       <c r="D89" t="s">
@@ -6243,7 +6160,7 @@
       <c r="I89">
         <v>640000</v>
       </c>
-      <c r="J89" s="38" t="s">
+      <c r="J89" s="19" t="s">
         <v>166</v>
       </c>
       <c r="K89" t="s">
@@ -6262,10 +6179,10 @@
         <f t="shared" si="0"/>
         <v>906</v>
       </c>
-      <c r="B90" s="40">
+      <c r="B90" s="20">
         <v>9</v>
       </c>
-      <c r="C90" s="28">
+      <c r="C90" s="21">
         <v>6</v>
       </c>
       <c r="D90" t="s">
@@ -6286,7 +6203,7 @@
       <c r="I90">
         <v>1280000</v>
       </c>
-      <c r="J90" s="38" t="s">
+      <c r="J90" s="19" t="s">
         <v>166</v>
       </c>
       <c r="K90" t="s">
@@ -6305,10 +6222,10 @@
         <f t="shared" si="0"/>
         <v>907</v>
       </c>
-      <c r="B91" s="40">
+      <c r="B91" s="20">
         <v>9</v>
       </c>
-      <c r="C91" s="28">
+      <c r="C91" s="21">
         <v>7</v>
       </c>
       <c r="D91" t="s">
@@ -6329,7 +6246,7 @@
       <c r="I91">
         <v>2560000</v>
       </c>
-      <c r="J91" s="38" t="s">
+      <c r="J91" s="19" t="s">
         <v>166</v>
       </c>
       <c r="K91" t="s">
@@ -6348,10 +6265,10 @@
         <f t="shared" si="0"/>
         <v>908</v>
       </c>
-      <c r="B92" s="40">
+      <c r="B92" s="20">
         <v>9</v>
       </c>
-      <c r="C92" s="28">
+      <c r="C92" s="21">
         <v>8</v>
       </c>
       <c r="D92" t="s">
@@ -6372,7 +6289,7 @@
       <c r="I92">
         <v>5120000</v>
       </c>
-      <c r="J92" s="38" t="s">
+      <c r="J92" s="19" t="s">
         <v>166</v>
       </c>
       <c r="K92" t="s">
@@ -6391,10 +6308,10 @@
         <f t="shared" ref="A93:A94" si="26">B93*100+C93</f>
         <v>909</v>
       </c>
-      <c r="B93" s="40">
+      <c r="B93" s="20">
         <v>9</v>
       </c>
-      <c r="C93" s="28">
+      <c r="C93" s="21">
         <v>9</v>
       </c>
       <c r="D93" t="s">
@@ -6415,7 +6332,7 @@
       <c r="I93">
         <v>10240000</v>
       </c>
-      <c r="J93" s="38" t="s">
+      <c r="J93" s="19" t="s">
         <v>166</v>
       </c>
       <c r="K93" t="s">
@@ -6434,10 +6351,10 @@
         <f t="shared" si="26"/>
         <v>910</v>
       </c>
-      <c r="B94" s="40">
+      <c r="B94" s="20">
         <v>9</v>
       </c>
-      <c r="C94" s="28">
+      <c r="C94" s="21">
         <v>10</v>
       </c>
       <c r="D94" t="s">
@@ -6458,7 +6375,7 @@
       <c r="I94">
         <v>20480000</v>
       </c>
-      <c r="J94" s="38" t="s">
+      <c r="J94" s="19" t="s">
         <v>166</v>
       </c>
       <c r="K94" t="s">
@@ -6472,217 +6389,217 @@
         <v>2048</v>
       </c>
     </row>
-    <row r="95" s="39" customFormat="1" spans="1:13">
+    <row r="95" s="18" customFormat="1" spans="1:13">
       <c r="A95">
         <f t="shared" si="0"/>
         <v>1001</v>
       </c>
-      <c r="B95" s="41">
+      <c r="B95" s="22">
         <v>10</v>
       </c>
-      <c r="C95" s="42">
+      <c r="C95" s="23">
         <v>1</v>
       </c>
-      <c r="D95" s="39" t="s">
+      <c r="D95" s="18" t="s">
         <v>176</v>
       </c>
-      <c r="E95" s="39" t="s">
+      <c r="E95" s="18" t="s">
         <v>177</v>
       </c>
-      <c r="F95" s="39" t="s">
+      <c r="F95" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="G95" s="39" t="s">
+      <c r="G95" s="18" t="s">
         <v>179</v>
       </c>
-      <c r="H95" s="39" t="s">
+      <c r="H95" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="I95" s="39">
+      <c r="I95" s="18">
         <v>5</v>
       </c>
-      <c r="J95" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="K95" s="39" t="s">
+      <c r="J95" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="K95" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="L95" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="M95" s="39">
+      <c r="L95" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="M95" s="18">
         <f>ROUND(I95-(2.5*(C95-1)),0)</f>
         <v>5</v>
       </c>
     </row>
-    <row r="96" s="39" customFormat="1" spans="1:13">
+    <row r="96" s="18" customFormat="1" spans="1:13">
       <c r="A96">
         <f t="shared" si="0"/>
         <v>1002</v>
       </c>
-      <c r="B96" s="41">
+      <c r="B96" s="22">
         <v>10</v>
       </c>
-      <c r="C96" s="42">
+      <c r="C96" s="23">
         <v>2</v>
       </c>
-      <c r="D96" s="39" t="s">
+      <c r="D96" s="18" t="s">
         <v>180</v>
       </c>
-      <c r="E96" s="39" t="s">
+      <c r="E96" s="18" t="s">
         <v>177</v>
       </c>
-      <c r="F96" s="39" t="s">
+      <c r="F96" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="G96" s="39" t="s">
+      <c r="G96" s="18" t="s">
         <v>179</v>
       </c>
-      <c r="H96" s="39" t="s">
+      <c r="H96" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="I96" s="39">
+      <c r="I96" s="18">
         <v>10</v>
       </c>
-      <c r="J96" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="K96" s="39" t="s">
+      <c r="J96" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="K96" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="L96" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="M96" s="39">
+      <c r="L96" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="M96" s="18">
         <f t="shared" ref="M96:M99" si="27">ROUND(I96-(2.5*(C96-1)),0)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="97" s="39" customFormat="1" spans="1:13">
+    <row r="97" s="18" customFormat="1" spans="1:13">
       <c r="A97">
         <f t="shared" si="0"/>
         <v>1003</v>
       </c>
-      <c r="B97" s="41">
+      <c r="B97" s="22">
         <v>10</v>
       </c>
-      <c r="C97" s="42">
+      <c r="C97" s="23">
         <v>3</v>
       </c>
-      <c r="D97" s="39" t="s">
+      <c r="D97" s="18" t="s">
         <v>181</v>
       </c>
-      <c r="E97" s="39" t="s">
+      <c r="E97" s="18" t="s">
         <v>177</v>
       </c>
-      <c r="F97" s="39" t="s">
+      <c r="F97" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="G97" s="39" t="s">
+      <c r="G97" s="18" t="s">
         <v>179</v>
       </c>
-      <c r="H97" s="39" t="s">
+      <c r="H97" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="I97" s="39">
+      <c r="I97" s="18">
         <v>20</v>
       </c>
-      <c r="J97" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="K97" s="39" t="s">
+      <c r="J97" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="K97" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="L97" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="M97" s="39">
+      <c r="L97" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="M97" s="18">
         <f t="shared" si="27"/>
         <v>15</v>
       </c>
     </row>
-    <row r="98" s="39" customFormat="1" spans="1:13">
+    <row r="98" s="18" customFormat="1" spans="1:13">
       <c r="A98">
         <f t="shared" ref="A98:A111" si="28">B98*100+C98</f>
         <v>1004</v>
       </c>
-      <c r="B98" s="41">
+      <c r="B98" s="22">
         <v>10</v>
       </c>
-      <c r="C98" s="42">
+      <c r="C98" s="23">
         <v>4</v>
       </c>
-      <c r="D98" s="39" t="s">
+      <c r="D98" s="18" t="s">
         <v>182</v>
       </c>
-      <c r="E98" s="39" t="s">
+      <c r="E98" s="18" t="s">
         <v>177</v>
       </c>
-      <c r="F98" s="39" t="s">
+      <c r="F98" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="G98" s="39" t="s">
+      <c r="G98" s="18" t="s">
         <v>179</v>
       </c>
-      <c r="H98" s="39" t="s">
+      <c r="H98" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="I98" s="39">
+      <c r="I98" s="18">
         <v>40</v>
       </c>
-      <c r="J98" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="K98" s="39" t="s">
+      <c r="J98" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="K98" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="L98" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="M98" s="39">
+      <c r="L98" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="M98" s="18">
         <f t="shared" si="27"/>
         <v>33</v>
       </c>
     </row>
-    <row r="99" s="39" customFormat="1" spans="1:13">
+    <row r="99" s="18" customFormat="1" spans="1:13">
       <c r="A99">
         <f t="shared" si="28"/>
         <v>1005</v>
       </c>
-      <c r="B99" s="41">
+      <c r="B99" s="22">
         <v>10</v>
       </c>
-      <c r="C99" s="42">
+      <c r="C99" s="23">
         <v>5</v>
       </c>
-      <c r="D99" s="39" t="s">
+      <c r="D99" s="18" t="s">
         <v>183</v>
       </c>
-      <c r="E99" s="39" t="s">
+      <c r="E99" s="18" t="s">
         <v>177</v>
       </c>
-      <c r="F99" s="39" t="s">
+      <c r="F99" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="G99" s="39" t="s">
+      <c r="G99" s="18" t="s">
         <v>179</v>
       </c>
-      <c r="H99" s="39" t="s">
+      <c r="H99" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="I99" s="39">
+      <c r="I99" s="18">
         <v>80</v>
       </c>
-      <c r="J99" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="K99" s="39" t="s">
+      <c r="J99" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="K99" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="L99" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="M99" s="39">
+      <c r="L99" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="M99" s="18">
         <f t="shared" si="27"/>
         <v>70</v>
       </c>
@@ -6692,22 +6609,22 @@
         <f t="shared" si="28"/>
         <v>1101</v>
       </c>
-      <c r="B100" s="40">
+      <c r="B100" s="20">
         <v>11</v>
       </c>
-      <c r="C100" s="28">
+      <c r="C100" s="21">
         <v>1</v>
       </c>
       <c r="D100" t="s">
         <v>184</v>
       </c>
-      <c r="E100" s="39" t="s">
+      <c r="E100" s="18" t="s">
         <v>185</v>
       </c>
       <c r="F100" t="s">
         <v>186</v>
       </c>
-      <c r="G100" s="39" t="s">
+      <c r="G100" s="18" t="s">
         <v>187</v>
       </c>
       <c r="H100" t="s">
@@ -6734,22 +6651,22 @@
         <f t="shared" si="28"/>
         <v>1102</v>
       </c>
-      <c r="B101" s="40">
+      <c r="B101" s="20">
         <v>11</v>
       </c>
-      <c r="C101" s="28">
+      <c r="C101" s="21">
         <v>2</v>
       </c>
       <c r="D101" t="s">
         <v>188</v>
       </c>
-      <c r="E101" s="39" t="s">
+      <c r="E101" s="18" t="s">
         <v>185</v>
       </c>
       <c r="F101" t="s">
         <v>189</v>
       </c>
-      <c r="G101" s="39" t="s">
+      <c r="G101" s="18" t="s">
         <v>187</v>
       </c>
       <c r="H101" t="s">
@@ -6776,22 +6693,22 @@
         <f t="shared" si="28"/>
         <v>1103</v>
       </c>
-      <c r="B102" s="40">
+      <c r="B102" s="20">
         <v>11</v>
       </c>
-      <c r="C102" s="28">
+      <c r="C102" s="21">
         <v>3</v>
       </c>
       <c r="D102" t="s">
         <v>190</v>
       </c>
-      <c r="E102" s="39" t="s">
+      <c r="E102" s="18" t="s">
         <v>185</v>
       </c>
       <c r="F102" t="s">
         <v>189</v>
       </c>
-      <c r="G102" s="39" t="s">
+      <c r="G102" s="18" t="s">
         <v>187</v>
       </c>
       <c r="H102" t="s">
@@ -6818,22 +6735,22 @@
         <f t="shared" si="28"/>
         <v>1104</v>
       </c>
-      <c r="B103" s="40">
+      <c r="B103" s="20">
         <v>11</v>
       </c>
-      <c r="C103" s="28">
+      <c r="C103" s="21">
         <v>4</v>
       </c>
       <c r="D103" t="s">
         <v>191</v>
       </c>
-      <c r="E103" s="39" t="s">
+      <c r="E103" s="18" t="s">
         <v>185</v>
       </c>
       <c r="F103" t="s">
         <v>189</v>
       </c>
-      <c r="G103" s="39" t="s">
+      <c r="G103" s="18" t="s">
         <v>187</v>
       </c>
       <c r="H103" t="s">
@@ -6855,171 +6772,171 @@
         <v>25</v>
       </c>
     </row>
-    <row r="104" s="39" customFormat="1" spans="1:13">
+    <row r="104" s="18" customFormat="1" spans="1:13">
       <c r="A104">
         <f t="shared" si="28"/>
         <v>1201</v>
       </c>
-      <c r="B104" s="41">
+      <c r="B104" s="22">
         <v>12</v>
       </c>
-      <c r="C104" s="42">
+      <c r="C104" s="23">
         <v>1</v>
       </c>
-      <c r="D104" s="39" t="s">
+      <c r="D104" s="18" t="s">
         <v>192</v>
       </c>
-      <c r="E104" s="39" t="s">
+      <c r="E104" s="18" t="s">
         <v>193</v>
       </c>
-      <c r="F104" s="39" t="s">
+      <c r="F104" s="18" t="s">
         <v>194</v>
       </c>
-      <c r="G104" s="39" t="s">
+      <c r="G104" s="18" t="s">
         <v>195</v>
       </c>
-      <c r="H104" s="39" t="s">
+      <c r="H104" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="I104" s="39">
+      <c r="I104" s="18">
         <v>1</v>
       </c>
-      <c r="J104" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="K104" s="39" t="s">
+      <c r="J104" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="K104" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="L104" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="M104" s="39">
+      <c r="L104" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="M104" s="18">
         <v>50</v>
       </c>
     </row>
-    <row r="105" s="39" customFormat="1" spans="1:13">
+    <row r="105" s="18" customFormat="1" spans="1:13">
       <c r="A105">
         <f t="shared" si="28"/>
         <v>1202</v>
       </c>
-      <c r="B105" s="41">
+      <c r="B105" s="22">
         <v>12</v>
       </c>
-      <c r="C105" s="42">
+      <c r="C105" s="23">
         <v>2</v>
       </c>
-      <c r="D105" s="39" t="s">
+      <c r="D105" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="E105" s="39" t="s">
+      <c r="E105" s="18" t="s">
         <v>193</v>
       </c>
-      <c r="F105" s="39" t="s">
+      <c r="F105" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="G105" s="39" t="s">
+      <c r="G105" s="18" t="s">
         <v>195</v>
       </c>
-      <c r="H105" s="39" t="s">
+      <c r="H105" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="I105" s="39">
+      <c r="I105" s="18">
         <v>2</v>
       </c>
-      <c r="J105" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="K105" s="39" t="s">
+      <c r="J105" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="K105" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="L105" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="M105" s="39">
+      <c r="L105" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="M105" s="18">
         <v>50</v>
       </c>
     </row>
-    <row r="106" s="39" customFormat="1" spans="1:13">
+    <row r="106" s="18" customFormat="1" spans="1:13">
       <c r="A106">
         <f t="shared" si="28"/>
         <v>1203</v>
       </c>
-      <c r="B106" s="41">
+      <c r="B106" s="22">
         <v>12</v>
       </c>
-      <c r="C106" s="42">
+      <c r="C106" s="23">
         <v>3</v>
       </c>
-      <c r="D106" s="39" t="s">
+      <c r="D106" s="18" t="s">
         <v>198</v>
       </c>
-      <c r="E106" s="39" t="s">
+      <c r="E106" s="18" t="s">
         <v>193</v>
       </c>
-      <c r="F106" s="39" t="s">
+      <c r="F106" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="G106" s="39" t="s">
+      <c r="G106" s="18" t="s">
         <v>195</v>
       </c>
-      <c r="H106" s="39" t="s">
+      <c r="H106" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="I106" s="39">
+      <c r="I106" s="18">
         <v>3</v>
       </c>
-      <c r="J106" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="K106" s="39" t="s">
+      <c r="J106" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="K106" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="L106" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="M106" s="39">
+      <c r="L106" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="M106" s="18">
         <v>50</v>
       </c>
     </row>
-    <row r="107" s="39" customFormat="1" spans="1:13">
+    <row r="107" s="18" customFormat="1" spans="1:13">
       <c r="A107">
         <f t="shared" si="28"/>
         <v>1204</v>
       </c>
-      <c r="B107" s="41">
+      <c r="B107" s="22">
         <v>12</v>
       </c>
-      <c r="C107" s="42">
+      <c r="C107" s="23">
         <v>4</v>
       </c>
-      <c r="D107" s="39" t="s">
+      <c r="D107" s="18" t="s">
         <v>199</v>
       </c>
-      <c r="E107" s="39" t="s">
+      <c r="E107" s="18" t="s">
         <v>193</v>
       </c>
-      <c r="F107" s="39" t="s">
+      <c r="F107" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="G107" s="39" t="s">
+      <c r="G107" s="18" t="s">
         <v>195</v>
       </c>
-      <c r="H107" s="39" t="s">
+      <c r="H107" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="I107" s="39">
+      <c r="I107" s="18">
         <v>4</v>
       </c>
-      <c r="J107" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="K107" s="39" t="s">
+      <c r="J107" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="K107" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="L107" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="M107" s="39">
+      <c r="L107" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="M107" s="18">
         <v>50</v>
       </c>
     </row>
@@ -7028,22 +6945,22 @@
         <f t="shared" si="28"/>
         <v>1301</v>
       </c>
-      <c r="B108" s="40">
+      <c r="B108" s="20">
         <v>13</v>
       </c>
-      <c r="C108" s="28">
+      <c r="C108" s="21">
         <v>1</v>
       </c>
       <c r="D108" t="s">
         <v>200</v>
       </c>
-      <c r="E108" s="39" t="s">
+      <c r="E108" s="18" t="s">
         <v>201</v>
       </c>
       <c r="F108" t="s">
         <v>202</v>
       </c>
-      <c r="G108" s="39" t="s">
+      <c r="G108" s="18" t="s">
         <v>203</v>
       </c>
       <c r="H108" t="s">
@@ -7052,7 +6969,7 @@
       <c r="I108">
         <v>1</v>
       </c>
-      <c r="J108" s="38" t="s">
+      <c r="J108" s="19" t="s">
         <v>103</v>
       </c>
       <c r="K108" t="s">
@@ -7070,22 +6987,22 @@
         <f t="shared" si="28"/>
         <v>1302</v>
       </c>
-      <c r="B109" s="40">
+      <c r="B109" s="20">
         <v>13</v>
       </c>
-      <c r="C109" s="28">
+      <c r="C109" s="21">
         <v>2</v>
       </c>
       <c r="D109" t="s">
         <v>204</v>
       </c>
-      <c r="E109" s="39" t="s">
+      <c r="E109" s="18" t="s">
         <v>201</v>
       </c>
       <c r="F109" t="s">
         <v>205</v>
       </c>
-      <c r="G109" s="39" t="s">
+      <c r="G109" s="18" t="s">
         <v>203</v>
       </c>
       <c r="H109" t="s">
@@ -7094,7 +7011,7 @@
       <c r="I109">
         <v>2</v>
       </c>
-      <c r="J109" s="38" t="s">
+      <c r="J109" s="19" t="s">
         <v>103</v>
       </c>
       <c r="K109" t="s">
@@ -7112,22 +7029,22 @@
         <f t="shared" si="28"/>
         <v>1303</v>
       </c>
-      <c r="B110" s="40">
+      <c r="B110" s="20">
         <v>13</v>
       </c>
-      <c r="C110" s="28">
+      <c r="C110" s="21">
         <v>3</v>
       </c>
       <c r="D110" t="s">
         <v>206</v>
       </c>
-      <c r="E110" s="39" t="s">
+      <c r="E110" s="18" t="s">
         <v>201</v>
       </c>
       <c r="F110" t="s">
         <v>205</v>
       </c>
-      <c r="G110" s="39" t="s">
+      <c r="G110" s="18" t="s">
         <v>203</v>
       </c>
       <c r="H110" t="s">
@@ -7136,7 +7053,7 @@
       <c r="I110">
         <v>3</v>
       </c>
-      <c r="J110" s="38" t="s">
+      <c r="J110" s="19" t="s">
         <v>103</v>
       </c>
       <c r="K110" t="s">
@@ -7154,22 +7071,22 @@
         <f t="shared" si="28"/>
         <v>1304</v>
       </c>
-      <c r="B111" s="40">
+      <c r="B111" s="20">
         <v>13</v>
       </c>
-      <c r="C111" s="28">
+      <c r="C111" s="21">
         <v>4</v>
       </c>
       <c r="D111" t="s">
         <v>207</v>
       </c>
-      <c r="E111" s="39" t="s">
+      <c r="E111" s="18" t="s">
         <v>201</v>
       </c>
       <c r="F111" t="s">
         <v>205</v>
       </c>
-      <c r="G111" s="39" t="s">
+      <c r="G111" s="18" t="s">
         <v>203</v>
       </c>
       <c r="H111" t="s">
@@ -7178,7 +7095,7 @@
       <c r="I111">
         <v>4</v>
       </c>
-      <c r="J111" s="38" t="s">
+      <c r="J111" s="19" t="s">
         <v>103</v>
       </c>
       <c r="K111" t="s">
@@ -7191,8 +7108,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="112" spans="3:3">
-      <c r="C112" s="28"/>
+    <row r="112" spans="1:13">
+      <c r="C112" s="21"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7205,7 +7122,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N31"/>
+  <dimension ref="A1:O31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -7221,73 +7138,77 @@
     <col min="12" max="12" width="21.4285714285714" customWidth="1"/>
     <col min="13" max="13" width="16" customWidth="1"/>
     <col min="14" max="14" width="6.71428571428571" customWidth="1"/>
+    <col min="15" max="15" width="16.4285714285714" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
-      <c r="A1" t="s">
+    <row r="1" spans="1:15">
+      <c r="A1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="3" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="3">
+      <c r="O1" s="3" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
+      <c r="A2" s="5">
         <v>1</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="6">
         <v>1</v>
       </c>
       <c r="C2" s="5">
         <v>1</v>
       </c>
-      <c r="D2" t="s">
-        <v>209</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="D2" s="3" t="s">
         <v>210</v>
       </c>
+      <c r="E2" s="3" t="s">
+        <v>211</v>
+      </c>
       <c r="F2" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="G2" t="s">
         <v>212</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>213</v>
       </c>
       <c r="H2" s="5" t="s">
         <v>1</v>
@@ -7301,120 +7222,124 @@
       <c r="K2" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="L2" s="5">
-        <v>0</v>
+      <c r="L2" s="5" t="s">
+        <v>103</v>
       </c>
       <c r="M2" s="5">
         <v>3</v>
       </c>
-      <c r="N2" s="29" t="b">
+      <c r="N2" s="5" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="6">
+      <c r="O2" s="3"/>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" s="5">
         <v>2</v>
       </c>
-      <c r="C3">
+      <c r="B3" s="4"/>
+      <c r="C3" s="3">
         <v>2</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="E3" t="s">
-        <v>210</v>
-      </c>
-      <c r="F3" t="s">
-        <v>214</v>
-      </c>
-      <c r="G3" t="s">
-        <v>212</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="H3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="3">
         <v>2</v>
       </c>
-      <c r="J3" t="s">
-        <v>103</v>
-      </c>
-      <c r="K3" t="s">
+      <c r="J3" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="M3" s="3">
+        <v>5</v>
+      </c>
+      <c r="N3" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="M3">
-        <v>5</v>
-      </c>
-      <c r="N3" s="30" t="b">
+      <c r="O3" s="3"/>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" s="5">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6"/>
+      <c r="C4" s="5">
+        <v>3</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="I4" s="5">
+        <v>4</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="M4" s="5">
+        <v>7</v>
+      </c>
+      <c r="N4" s="5" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="7">
-        <v>3</v>
-      </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="9">
-        <v>3</v>
-      </c>
-      <c r="D4" t="s">
-        <v>215</v>
-      </c>
-      <c r="E4" t="s">
-        <v>210</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>214</v>
-      </c>
-      <c r="G4" t="s">
-        <v>212</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="I4" s="9">
+      <c r="O4" s="3"/>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" s="5">
         <v>4</v>
       </c>
-      <c r="J4" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="L4" s="9">
-        <v>0</v>
-      </c>
-      <c r="M4" s="9">
-        <v>7</v>
-      </c>
-      <c r="N4" s="31" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" s="3">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4">
+      <c r="B5" s="6">
         <v>2</v>
       </c>
       <c r="C5" s="5">
         <v>1</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="E5" t="s">
         <v>217</v>
       </c>
+      <c r="E5" s="3" t="s">
+        <v>218</v>
+      </c>
       <c r="F5" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="G5" t="s">
         <v>219</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>220</v>
       </c>
       <c r="H5" s="5" t="s">
         <v>5</v>
@@ -7434,241 +7359,248 @@
       <c r="M5" s="5">
         <v>2</v>
       </c>
-      <c r="N5" s="29" t="b">
+      <c r="N5" s="5" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="6">
+      <c r="O5" s="3"/>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" s="5">
         <v>5</v>
       </c>
-      <c r="C6">
+      <c r="B6" s="4"/>
+      <c r="C6" s="3">
         <v>2</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="E6" t="s">
-        <v>217</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="H6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I6" s="3">
+        <v>2</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M6" s="3">
+        <v>4</v>
+      </c>
+      <c r="N6" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="O6" s="3"/>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" s="5">
+        <v>6</v>
+      </c>
+      <c r="B7" s="6"/>
+      <c r="C7" s="5">
+        <v>3</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="G6" t="s">
+      <c r="F7" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="H6" t="s">
+      <c r="G7" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="H7" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="I6">
+      <c r="I7" s="5">
+        <v>4</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="M7" s="5">
+        <v>6</v>
+      </c>
+      <c r="N7" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="O7" s="3"/>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:15">
+      <c r="A8" s="7">
+        <v>7</v>
+      </c>
+      <c r="B8" s="8">
+        <v>3</v>
+      </c>
+      <c r="C8" s="7">
+        <v>1</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="I8" s="7">
+        <v>1</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="M8" s="7">
         <v>2</v>
       </c>
-      <c r="J6" t="s">
-        <v>103</v>
-      </c>
-      <c r="K6" t="s">
+      <c r="N8" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="O8" s="9"/>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:15">
+      <c r="A9" s="7">
+        <v>8</v>
+      </c>
+      <c r="B9" s="10"/>
+      <c r="C9" s="9">
+        <v>2</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="I9" s="9">
+        <v>2</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="K9" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="L6" t="s">
-        <v>39</v>
-      </c>
-      <c r="M6">
+      <c r="L9" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="M9" s="9">
         <v>4</v>
       </c>
-      <c r="N6" s="30" t="b">
+      <c r="N9" s="7" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="7">
+      <c r="O9" s="9"/>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:15">
+      <c r="A10" s="7">
+        <v>9</v>
+      </c>
+      <c r="B10" s="8"/>
+      <c r="C10" s="7">
+        <v>3</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="I10" s="7">
+        <v>4</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="M10" s="7">
         <v>6</v>
       </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="9">
-        <v>3</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>221</v>
-      </c>
-      <c r="E7" t="s">
-        <v>217</v>
-      </c>
-      <c r="F7" t="s">
-        <v>218</v>
-      </c>
-      <c r="G7" t="s">
-        <v>219</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="I7" s="9">
-        <v>4</v>
-      </c>
-      <c r="J7" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="K7" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="L7" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M7" s="9">
-        <v>6</v>
-      </c>
-      <c r="N7" s="31" t="b">
+      <c r="N10" s="7" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" s="1" customFormat="1" spans="1:14">
-      <c r="A8" s="10">
-        <v>7</v>
-      </c>
-      <c r="B8" s="11">
-        <v>3</v>
-      </c>
-      <c r="C8" s="12">
-        <v>1</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>224</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="H8" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="I8" s="12">
-        <v>1</v>
-      </c>
-      <c r="J8" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="K8" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="L8" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="M8" s="12">
-        <v>2</v>
-      </c>
-      <c r="N8" s="32" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" spans="1:14">
-      <c r="A9" s="13">
-        <v>8</v>
-      </c>
-      <c r="B9" s="14"/>
-      <c r="C9" s="1">
-        <v>2</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I9" s="1">
-        <v>2</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="M9" s="1">
-        <v>4</v>
-      </c>
-      <c r="N9" s="33" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" spans="1:14">
-      <c r="A10" s="15">
-        <v>9</v>
-      </c>
-      <c r="B10" s="16"/>
-      <c r="C10" s="17">
-        <v>3</v>
-      </c>
-      <c r="D10" s="17" t="s">
-        <v>227</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F10" s="17" t="s">
-        <v>224</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="H10" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="I10" s="17">
-        <v>4</v>
-      </c>
-      <c r="J10" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="K10" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="L10" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="M10" s="17">
-        <v>6</v>
-      </c>
-      <c r="N10" s="34" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="3">
+      <c r="O10" s="9"/>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" s="5">
         <v>10</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11" s="6">
         <v>4</v>
       </c>
       <c r="C11" s="5">
         <v>1</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="E11" s="18" t="s">
+        <v>229</v>
+      </c>
+      <c r="E11" s="11" t="s">
         <v>100</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="G11" s="18" t="s">
+        <v>230</v>
+      </c>
+      <c r="G11" s="11" t="s">
         <v>102</v>
       </c>
       <c r="H11" s="5" t="s">
@@ -7689,226 +7621,233 @@
       <c r="M11" s="5">
         <v>2</v>
       </c>
-      <c r="N11" s="29" t="b">
+      <c r="N11" s="5" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="6">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" s="5">
         <v>11</v>
       </c>
-      <c r="C12">
+      <c r="B12" s="4"/>
+      <c r="C12" s="3">
         <v>2</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="E12" s="18" t="s">
+      <c r="G12" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I12" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M12" s="3">
+        <v>4</v>
+      </c>
+      <c r="N12" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="O12" s="3"/>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" s="5">
+        <v>12</v>
+      </c>
+      <c r="B13" s="6"/>
+      <c r="C13" s="5">
+        <v>3</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="E13" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="F12" t="s">
-        <v>229</v>
-      </c>
-      <c r="G12" s="18" t="s">
+      <c r="F13" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="G13" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="H12" t="s">
+      <c r="H13" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="I12">
-        <v>1000</v>
-      </c>
-      <c r="J12" t="s">
-        <v>103</v>
-      </c>
-      <c r="K12" t="s">
+      <c r="I13" s="5">
+        <v>1500</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="K13" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="L12" t="s">
-        <v>39</v>
-      </c>
-      <c r="M12">
+      <c r="L13" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="M13" s="5">
+        <v>6</v>
+      </c>
+      <c r="N13" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3"/>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14" s="12">
+        <v>16</v>
+      </c>
+      <c r="B14" s="13">
+        <v>5</v>
+      </c>
+      <c r="C14" s="12">
+        <v>1</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>234</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="G14" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="H14" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="I14" s="12">
+        <v>2</v>
+      </c>
+      <c r="J14" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="K14" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="L14" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="M14" s="12">
         <v>4</v>
       </c>
-      <c r="N12" s="30" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="7">
+      <c r="N14" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="O14" s="3"/>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="A15" s="12">
+        <v>17</v>
+      </c>
+      <c r="B15" s="15"/>
+      <c r="C15" s="14">
+        <v>2</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>234</v>
+      </c>
+      <c r="F15" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="G15" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="H15" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="I15" s="14">
+        <v>4</v>
+      </c>
+      <c r="J15" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="K15" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="L15" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="M15" s="14">
+        <v>8</v>
+      </c>
+      <c r="N15" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="O15" s="3"/>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" s="12">
+        <v>18</v>
+      </c>
+      <c r="B16" s="13"/>
+      <c r="C16" s="12">
+        <v>3</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>234</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="G16" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="H16" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="I16" s="12">
+        <v>6</v>
+      </c>
+      <c r="J16" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="K16" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="L16" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="M16" s="12">
         <v>12</v>
       </c>
-      <c r="B13" s="8"/>
-      <c r="C13" s="9">
-        <v>3</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="E13" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>229</v>
-      </c>
-      <c r="G13" s="18" t="s">
-        <v>102</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="I13" s="9">
-        <v>1500</v>
-      </c>
-      <c r="J13" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="K13" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="L13" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M13" s="9">
-        <v>6</v>
-      </c>
-      <c r="N13" s="31" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14" s="19">
-        <v>16</v>
-      </c>
-      <c r="B14" s="20">
-        <v>5</v>
-      </c>
-      <c r="C14" s="21">
+      <c r="N16" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="D14" s="21" t="s">
-        <v>232</v>
-      </c>
-      <c r="E14" s="22" t="s">
-        <v>233</v>
-      </c>
-      <c r="F14" s="21" t="s">
-        <v>234</v>
-      </c>
-      <c r="G14" s="22" t="s">
-        <v>235</v>
-      </c>
-      <c r="H14" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="I14" s="21">
-        <v>2</v>
-      </c>
-      <c r="J14" s="21" t="s">
-        <v>103</v>
-      </c>
-      <c r="K14" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="L14" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="M14" s="21">
-        <v>4</v>
-      </c>
-      <c r="N14" s="35" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="A15" s="23">
-        <v>17</v>
-      </c>
-      <c r="B15" s="24"/>
-      <c r="C15" s="22">
-        <v>2</v>
-      </c>
-      <c r="D15" s="22" t="s">
-        <v>236</v>
-      </c>
-      <c r="E15" s="22" t="s">
-        <v>233</v>
-      </c>
-      <c r="F15" s="22" t="s">
-        <v>234</v>
-      </c>
-      <c r="G15" s="22" t="s">
-        <v>235</v>
-      </c>
-      <c r="H15" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="I15" s="22">
-        <v>4</v>
-      </c>
-      <c r="J15" s="22" t="s">
-        <v>103</v>
-      </c>
-      <c r="K15" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="L15" s="22" t="s">
-        <v>39</v>
-      </c>
-      <c r="M15" s="22">
-        <v>8</v>
-      </c>
-      <c r="N15" s="36" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="A16" s="25">
-        <v>18</v>
-      </c>
-      <c r="B16" s="26"/>
-      <c r="C16" s="27">
-        <v>3</v>
-      </c>
-      <c r="D16" s="27" t="s">
-        <v>237</v>
-      </c>
-      <c r="E16" s="22" t="s">
-        <v>233</v>
-      </c>
-      <c r="F16" s="27" t="s">
-        <v>234</v>
-      </c>
-      <c r="G16" s="22" t="s">
-        <v>235</v>
-      </c>
-      <c r="H16" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="I16" s="27">
-        <v>6</v>
-      </c>
-      <c r="J16" s="27" t="s">
-        <v>103</v>
-      </c>
-      <c r="K16" s="27" t="s">
-        <v>38</v>
-      </c>
-      <c r="L16" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="M16" s="27">
-        <v>12</v>
-      </c>
-      <c r="N16" s="37" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
-      <c r="A17" s="3">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="1:15">
+      <c r="A17" s="5">
         <v>19</v>
       </c>
-      <c r="B17" s="4">
+      <c r="B17" s="6">
         <v>6</v>
       </c>
       <c r="C17" s="5">
@@ -7917,13 +7856,13 @@
       <c r="D17" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" s="3" t="s">
         <v>150</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="G17" t="s">
+      <c r="G17" s="3" t="s">
         <v>152</v>
       </c>
       <c r="H17" s="5" t="s">
@@ -7944,241 +7883,248 @@
       <c r="M17" s="5">
         <v>2</v>
       </c>
-      <c r="N17" s="29" t="b">
+      <c r="N17" s="5" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:14">
-      <c r="A18" s="6">
+      <c r="O17" s="3"/>
+    </row>
+    <row r="18" spans="1:15">
+      <c r="A18" s="5">
         <v>20</v>
       </c>
-      <c r="C18">
+      <c r="B18" s="4"/>
+      <c r="C18" s="3">
         <v>2</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F18" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="G18" t="s">
+      <c r="G18" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="H18" t="s">
+      <c r="H18" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="3">
         <v>50</v>
       </c>
-      <c r="J18" t="s">
-        <v>39</v>
-      </c>
-      <c r="K18" t="s">
+      <c r="J18" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="K18" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="L18" t="s">
-        <v>39</v>
-      </c>
-      <c r="M18">
+      <c r="L18" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M18" s="3">
         <v>4</v>
       </c>
-      <c r="N18" s="30" t="b">
+      <c r="N18" s="5" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:14">
-      <c r="A19" s="7">
+      <c r="O18" s="3"/>
+    </row>
+    <row r="19" spans="1:15">
+      <c r="A19" s="5">
         <v>21</v>
       </c>
-      <c r="B19" s="8"/>
-      <c r="C19" s="9">
+      <c r="B19" s="6"/>
+      <c r="C19" s="5">
         <v>3</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="D19" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="F19" s="9" t="s">
+      <c r="F19" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="G19" t="s">
+      <c r="G19" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="H19" s="9" t="s">
+      <c r="H19" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I19" s="9">
+      <c r="I19" s="5">
         <v>100</v>
       </c>
-      <c r="J19" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="K19" s="9" t="s">
+      <c r="J19" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="K19" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="L19" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M19" s="9">
+      <c r="L19" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="M19" s="5">
         <v>6</v>
       </c>
-      <c r="N19" s="31" t="b">
+      <c r="N19" s="5" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" s="1" customFormat="1" spans="1:14">
-      <c r="A20" s="10">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" s="1" customFormat="1" spans="1:15">
+      <c r="A20" s="7">
         <v>22</v>
       </c>
-      <c r="B20" s="11">
+      <c r="B20" s="8">
         <v>7</v>
       </c>
-      <c r="C20" s="12">
+      <c r="C20" s="7">
         <v>1</v>
       </c>
-      <c r="D20" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="E20" s="1" t="s">
+      <c r="D20" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="F20" s="12" t="s">
+      <c r="E20" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="G20" s="1" t="s">
+      <c r="F20" s="7" t="s">
         <v>241</v>
       </c>
-      <c r="H20" s="12" t="s">
+      <c r="G20" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="H20" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="I20" s="12">
+      <c r="I20" s="7">
         <v>15</v>
       </c>
-      <c r="J20" s="12" t="s">
+      <c r="J20" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="L20" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="M20" s="7">
+        <v>3</v>
+      </c>
+      <c r="N20" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="O20" s="9"/>
+    </row>
+    <row r="21" s="1" customFormat="1" spans="1:15">
+      <c r="A21" s="7">
+        <v>23</v>
+      </c>
+      <c r="B21" s="10"/>
+      <c r="C21" s="9">
+        <v>2</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="G21" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="K20" s="12" t="s">
+      <c r="H21" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I21" s="9">
+        <v>30</v>
+      </c>
+      <c r="J21" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="K21" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="L20" s="12">
+      <c r="L21" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="M21" s="9">
+        <v>5</v>
+      </c>
+      <c r="N21" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="M20" s="12">
+      <c r="O21" s="9"/>
+    </row>
+    <row r="22" s="1" customFormat="1" spans="1:15">
+      <c r="A22" s="7">
+        <v>24</v>
+      </c>
+      <c r="B22" s="8"/>
+      <c r="C22" s="7">
         <v>3</v>
       </c>
-      <c r="N20" s="32" t="b">
+      <c r="D22" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="I22" s="7">
+        <v>60</v>
+      </c>
+      <c r="J22" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="L22" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="M22" s="7">
+        <v>7</v>
+      </c>
+      <c r="N22" s="7" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" s="1" customFormat="1" spans="1:14">
-      <c r="A21" s="13">
-        <v>23</v>
-      </c>
-      <c r="B21" s="14"/>
-      <c r="C21" s="1">
-        <v>2</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I21" s="1">
-        <v>30</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="L21" s="1">
-        <v>0</v>
-      </c>
-      <c r="M21" s="1">
-        <v>5</v>
-      </c>
-      <c r="N21" s="33" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" s="1" customFormat="1" spans="1:14">
-      <c r="A22" s="15">
-        <v>24</v>
-      </c>
-      <c r="B22" s="16"/>
-      <c r="C22" s="17">
-        <v>3</v>
-      </c>
-      <c r="D22" s="17" t="s">
-        <v>244</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="F22" s="17" t="s">
-        <v>240</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="H22" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="I22" s="17">
-        <v>60</v>
-      </c>
-      <c r="J22" s="17" t="s">
-        <v>242</v>
-      </c>
-      <c r="K22" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="L22" s="17">
-        <v>0</v>
-      </c>
-      <c r="M22" s="17">
-        <v>7</v>
-      </c>
-      <c r="N22" s="34" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14">
-      <c r="A23" s="3">
+      <c r="O22" s="9"/>
+    </row>
+    <row r="23" spans="1:15">
+      <c r="A23" s="5">
         <v>25</v>
       </c>
-      <c r="B23" s="4">
+      <c r="B23" s="6">
         <v>8</v>
       </c>
       <c r="C23" s="5">
         <v>1</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="E23" s="18" t="s">
+        <v>246</v>
+      </c>
+      <c r="E23" s="11" t="s">
         <v>177</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="G23" s="18" t="s">
+        <v>247</v>
+      </c>
+      <c r="G23" s="11" t="s">
         <v>179</v>
       </c>
       <c r="H23" s="5" t="s">
@@ -8194,103 +8140,107 @@
         <v>38</v>
       </c>
       <c r="L23" s="5" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M23" s="5">
         <v>2</v>
       </c>
-      <c r="N23" s="29" t="b">
+      <c r="N23" s="5" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:14">
-      <c r="A24" s="6">
+      <c r="O23" s="3"/>
+    </row>
+    <row r="24" spans="1:15">
+      <c r="A24" s="5">
         <v>26</v>
       </c>
-      <c r="C24">
+      <c r="B24" s="4"/>
+      <c r="C24" s="3">
         <v>2</v>
       </c>
-      <c r="D24" t="s">
-        <v>247</v>
-      </c>
-      <c r="E24" s="18" t="s">
+      <c r="D24" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="E24" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F24" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="G24" s="18" t="s">
+      <c r="G24" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="H24" t="s">
+      <c r="H24" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="I24">
+      <c r="I24" s="3">
         <v>8</v>
       </c>
-      <c r="J24" t="s">
-        <v>103</v>
-      </c>
-      <c r="K24" t="s">
+      <c r="J24" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="K24" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="L24" t="s">
-        <v>242</v>
-      </c>
-      <c r="M24">
+      <c r="L24" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="M24" s="3">
         <v>4</v>
       </c>
-      <c r="N24" s="30" t="b">
+      <c r="N24" s="5" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:14">
-      <c r="A25" s="7">
+      <c r="O24" s="3"/>
+    </row>
+    <row r="25" spans="1:15">
+      <c r="A25" s="5">
         <v>27</v>
       </c>
-      <c r="B25" s="8"/>
-      <c r="C25" s="9">
+      <c r="B25" s="6"/>
+      <c r="C25" s="5">
         <v>3</v>
       </c>
-      <c r="D25" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="E25" s="18" t="s">
+      <c r="D25" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="E25" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="F25" s="9" t="s">
+      <c r="F25" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="G25" s="18" t="s">
+      <c r="G25" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="H25" s="9" t="s">
+      <c r="H25" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="I25" s="9">
+      <c r="I25" s="5">
         <v>12</v>
       </c>
-      <c r="J25" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="K25" s="9" t="s">
+      <c r="J25" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="K25" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="L25" s="9" t="s">
-        <v>242</v>
-      </c>
-      <c r="M25" s="9">
+      <c r="L25" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="M25" s="5">
         <v>6</v>
       </c>
-      <c r="N25" s="31" t="b">
+      <c r="N25" s="5" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:14">
-      <c r="A26" s="3">
+      <c r="O25" s="3"/>
+    </row>
+    <row r="26" spans="1:15">
+      <c r="A26" s="5">
         <v>28</v>
       </c>
-      <c r="B26" s="4">
+      <c r="B26" s="6">
         <v>9</v>
       </c>
       <c r="C26" s="5">
@@ -8299,13 +8249,13 @@
       <c r="D26" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="E26" s="18" t="s">
+      <c r="E26" s="11" t="s">
         <v>123</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="G26" s="18" t="s">
+      <c r="G26" s="11" t="s">
         <v>125</v>
       </c>
       <c r="H26" s="5" t="s">
@@ -8320,224 +8270,233 @@
       <c r="K26" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="L26" s="5">
-        <v>0</v>
+      <c r="L26" s="5" t="s">
+        <v>103</v>
       </c>
       <c r="M26" s="5">
         <v>3</v>
       </c>
-      <c r="N26" s="29" t="b">
+      <c r="N26" s="5" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:14">
-      <c r="A27" s="6">
+      <c r="O26" s="3"/>
+    </row>
+    <row r="27" spans="1:15">
+      <c r="A27" s="5">
         <v>29</v>
       </c>
-      <c r="C27">
+      <c r="B27" s="4"/>
+      <c r="C27" s="3">
         <v>2</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D27" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="E27" s="18" t="s">
+      <c r="E27" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="F27" t="s">
+      <c r="F27" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="G27" s="18" t="s">
+      <c r="G27" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="H27" t="s">
+      <c r="H27" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="I27">
+      <c r="I27" s="3">
         <v>12</v>
       </c>
-      <c r="J27" t="s">
-        <v>103</v>
-      </c>
-      <c r="K27" t="s">
+      <c r="J27" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="K27" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="L27">
+      <c r="L27" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="M27" s="3">
+        <v>5</v>
+      </c>
+      <c r="N27" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="M27">
-        <v>5</v>
-      </c>
-      <c r="N27" s="30" t="b">
+      <c r="O27" s="3"/>
+    </row>
+    <row r="28" spans="1:15">
+      <c r="A28" s="5">
+        <v>30</v>
+      </c>
+      <c r="B28" s="6"/>
+      <c r="C28" s="5">
+        <v>3</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="G28" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I28" s="5">
+        <v>18</v>
+      </c>
+      <c r="J28" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="K28" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="L28" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="M28" s="5">
+        <v>7</v>
+      </c>
+      <c r="N28" s="5" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:14">
-      <c r="A28" s="7">
-        <v>30</v>
-      </c>
-      <c r="B28" s="8"/>
-      <c r="C28" s="9">
-        <v>3</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="E28" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="F28" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="G28" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="H28" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="I28" s="9">
-        <v>18</v>
-      </c>
-      <c r="J28" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="K28" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="L28" s="9">
-        <v>0</v>
-      </c>
-      <c r="M28" s="9">
+      <c r="O28" s="3"/>
+    </row>
+    <row r="29" spans="1:15">
+      <c r="A29" s="3">
+        <v>31</v>
+      </c>
+      <c r="B29" s="4">
+        <v>10</v>
+      </c>
+      <c r="C29" s="16">
+        <v>1</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I29" s="3">
         <v>7</v>
       </c>
-      <c r="N28" s="31" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14">
-      <c r="A29">
-        <v>31</v>
-      </c>
-      <c r="B29" s="2">
-        <v>10</v>
-      </c>
-      <c r="C29" s="28">
-        <v>1</v>
-      </c>
-      <c r="D29" t="s">
-        <v>136</v>
-      </c>
-      <c r="E29" t="s">
-        <v>137</v>
-      </c>
-      <c r="F29" t="s">
-        <v>138</v>
-      </c>
-      <c r="G29" t="s">
-        <v>139</v>
-      </c>
-      <c r="H29" t="s">
-        <v>16</v>
-      </c>
-      <c r="I29">
-        <v>7</v>
-      </c>
-      <c r="J29" s="38" t="s">
+      <c r="J29" s="17" t="s">
         <v>103</v>
       </c>
       <c r="K29" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="L29" s="5">
-        <v>0</v>
+      <c r="L29" s="5" t="s">
+        <v>103</v>
       </c>
       <c r="M29" s="5">
         <v>3</v>
       </c>
-      <c r="N29" s="29" t="b">
+      <c r="N29" s="5" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:14">
-      <c r="A30">
+      <c r="O29" s="3"/>
+    </row>
+    <row r="30" spans="1:15">
+      <c r="A30" s="3">
         <v>32</v>
       </c>
-      <c r="C30" s="28">
+      <c r="B30" s="4"/>
+      <c r="C30" s="16">
         <v>2</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D30" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E30" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="F30" t="s">
+      <c r="F30" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="G30" t="s">
+      <c r="G30" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="H30" t="s">
+      <c r="H30" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I30">
+      <c r="I30" s="3">
         <v>14</v>
       </c>
-      <c r="J30" s="38" t="s">
-        <v>103</v>
-      </c>
-      <c r="K30" t="s">
+      <c r="J30" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="K30" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="L30">
+      <c r="L30" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="M30" s="3">
+        <v>5</v>
+      </c>
+      <c r="N30" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="M30">
-        <v>5</v>
-      </c>
-      <c r="N30" s="30" t="b">
+      <c r="O30" s="3"/>
+    </row>
+    <row r="31" spans="1:15">
+      <c r="A31" s="3">
+        <v>33</v>
+      </c>
+      <c r="B31" s="4"/>
+      <c r="C31" s="16">
+        <v>3</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I31" s="3">
+        <v>21</v>
+      </c>
+      <c r="J31" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="K31" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="L31" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="M31" s="5">
+        <v>7</v>
+      </c>
+      <c r="N31" s="5" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:14">
-      <c r="A31">
-        <v>33</v>
-      </c>
-      <c r="C31" s="28">
-        <v>3</v>
-      </c>
-      <c r="D31" t="s">
-        <v>141</v>
-      </c>
-      <c r="E31" t="s">
-        <v>137</v>
-      </c>
-      <c r="F31" t="s">
-        <v>138</v>
-      </c>
-      <c r="G31" t="s">
-        <v>139</v>
-      </c>
-      <c r="H31" t="s">
-        <v>16</v>
-      </c>
-      <c r="I31">
-        <v>21</v>
-      </c>
-      <c r="J31" s="38" t="s">
-        <v>103</v>
-      </c>
-      <c r="K31" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="L31" s="9">
-        <v>0</v>
-      </c>
-      <c r="M31" s="9">
-        <v>7</v>
-      </c>
-      <c r="N31" s="31" t="b">
-        <v>0</v>
-      </c>
+      <c r="O31" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="10">
